--- a/testdata/fictief/Lijst_FvB_20260901.xlsx
+++ b/testdata/fictief/Lijst_FvB_20260901.xlsx
@@ -55,28 +55,34 @@
     <t>Chen Kortenhoeven</t>
   </si>
   <si>
+    <t>Coördinator</t>
+  </si>
+  <si>
+    <t>Dewi Kloosterboer</t>
+  </si>
+  <si>
+    <t>dewi.kloosterboer@bloeij.example</t>
+  </si>
+  <si>
+    <t>Medewerker</t>
+  </si>
+  <si>
+    <t>Anouk Nieuwland</t>
+  </si>
+  <si>
+    <t>anouk.nieuwland@bloeij.example</t>
+  </si>
+  <si>
     <t>Adviseur</t>
   </si>
   <si>
-    <t>Dewi Kloosterboer</t>
-  </si>
-  <si>
-    <t>dewi.kloosterboer@bloeij.example</t>
-  </si>
-  <si>
-    <t>Anouk Nieuwland</t>
-  </si>
-  <si>
-    <t>anouk.nieuwland@bloeij.example</t>
-  </si>
-  <si>
     <t>Hatice van Dijkhoff</t>
   </si>
   <si>
     <t>hatice.vandijkhoff@bloeij.example</t>
   </si>
   <si>
-    <t>Coördinator</t>
+    <t>Specialist</t>
   </si>
   <si>
     <t>Wout van Zandbergen</t>
@@ -85,9 +91,6 @@
     <t>wout.vanzandbergen@bloeij.example</t>
   </si>
   <si>
-    <t>Specialist</t>
-  </si>
-  <si>
     <t>Niels van der Rietveld</t>
   </si>
   <si>
@@ -112,28 +115,25 @@
     <t>niels.vanderdijkhoff@bloeij.example</t>
   </si>
   <si>
-    <t>Medewerker</t>
-  </si>
-  <si>
     <t>Joost ter Kloosterboer</t>
   </si>
   <si>
     <t>joost.terkloosterboer@bloeij.example</t>
   </si>
   <si>
+    <t>Noor Kloosterboer</t>
+  </si>
+  <si>
+    <t>noor.kloosterboer@bloeij.example</t>
+  </si>
+  <si>
+    <t>Daan van Akkerman</t>
+  </si>
+  <si>
+    <t>daan.vanakkerman@bloeij.example</t>
+  </si>
+  <si>
     <t>Senior medewerker</t>
-  </si>
-  <si>
-    <t>Noor Kloosterboer</t>
-  </si>
-  <si>
-    <t>noor.kloosterboer@bloeij.example</t>
-  </si>
-  <si>
-    <t>Daan van Akkerman</t>
-  </si>
-  <si>
-    <t>daan.vanakkerman@bloeij.example</t>
   </si>
   <si>
     <t>Tessa de Hofstede</t>
@@ -6490,7 +6490,7 @@
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -6498,10 +6498,10 @@
         <v>100002</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
@@ -6513,7 +6513,7 @@
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -6521,10 +6521,10 @@
         <v>100003</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
@@ -6536,7 +6536,7 @@
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -6544,10 +6544,10 @@
         <v>100004</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
@@ -6559,7 +6559,7 @@
         <v>13</v>
       </c>
       <c r="G9" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -6567,10 +6567,10 @@
         <v>100005</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
@@ -6582,7 +6582,7 @@
         <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -6590,10 +6590,10 @@
         <v>100006</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -6605,7 +6605,7 @@
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -6613,10 +6613,10 @@
         <v>100007</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
@@ -6628,7 +6628,7 @@
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -6636,10 +6636,10 @@
         <v>100008</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
@@ -6651,7 +6651,7 @@
         <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -6674,7 +6674,7 @@
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -6682,10 +6682,10 @@
         <v>100010</v>
       </c>
       <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" t="s">
         <v>37</v>
-      </c>
-      <c r="C15" t="s">
-        <v>38</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
@@ -6697,7 +6697,7 @@
         <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -6705,10 +6705,10 @@
         <v>100011</v>
       </c>
       <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" t="s">
         <v>39</v>
-      </c>
-      <c r="C16" t="s">
-        <v>40</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
@@ -6720,7 +6720,7 @@
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -6743,7 +6743,7 @@
         <v>13</v>
       </c>
       <c r="G17" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -6766,7 +6766,7 @@
         <v>46</v>
       </c>
       <c r="G18" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -6789,7 +6789,7 @@
         <v>50</v>
       </c>
       <c r="G19" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -6812,7 +6812,7 @@
         <v>54</v>
       </c>
       <c r="G20" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -6835,7 +6835,7 @@
         <v>54</v>
       </c>
       <c r="G21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -6858,7 +6858,7 @@
         <v>54</v>
       </c>
       <c r="G22" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -6881,7 +6881,7 @@
         <v>54</v>
       </c>
       <c r="G23" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -6904,7 +6904,7 @@
         <v>54</v>
       </c>
       <c r="G24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -6927,7 +6927,7 @@
         <v>54</v>
       </c>
       <c r="G25" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -6950,7 +6950,7 @@
         <v>54</v>
       </c>
       <c r="G26" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -6973,7 +6973,7 @@
         <v>54</v>
       </c>
       <c r="G27" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -6996,7 +6996,7 @@
         <v>54</v>
       </c>
       <c r="G28" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -7019,7 +7019,7 @@
         <v>54</v>
       </c>
       <c r="G29" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -7042,7 +7042,7 @@
         <v>54</v>
       </c>
       <c r="G30" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -7065,7 +7065,7 @@
         <v>54</v>
       </c>
       <c r="G31" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -7088,7 +7088,7 @@
         <v>54</v>
       </c>
       <c r="G32" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -7111,7 +7111,7 @@
         <v>54</v>
       </c>
       <c r="G33" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -7134,7 +7134,7 @@
         <v>54</v>
       </c>
       <c r="G34" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -7157,7 +7157,7 @@
         <v>54</v>
       </c>
       <c r="G35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -7180,7 +7180,7 @@
         <v>54</v>
       </c>
       <c r="G36" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -7203,7 +7203,7 @@
         <v>54</v>
       </c>
       <c r="G37" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -7226,7 +7226,7 @@
         <v>54</v>
       </c>
       <c r="G38" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -7249,7 +7249,7 @@
         <v>54</v>
       </c>
       <c r="G39" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -7272,7 +7272,7 @@
         <v>54</v>
       </c>
       <c r="G40" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -7295,7 +7295,7 @@
         <v>98</v>
       </c>
       <c r="G41" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -7318,7 +7318,7 @@
         <v>98</v>
       </c>
       <c r="G42" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -7341,7 +7341,7 @@
         <v>98</v>
       </c>
       <c r="G43" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -7364,7 +7364,7 @@
         <v>98</v>
       </c>
       <c r="G44" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -7387,7 +7387,7 @@
         <v>98</v>
       </c>
       <c r="G45" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -7410,7 +7410,7 @@
         <v>98</v>
       </c>
       <c r="G46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -7433,7 +7433,7 @@
         <v>98</v>
       </c>
       <c r="G47" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -7456,7 +7456,7 @@
         <v>98</v>
       </c>
       <c r="G48" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -7479,7 +7479,7 @@
         <v>98</v>
       </c>
       <c r="G49" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -7502,7 +7502,7 @@
         <v>98</v>
       </c>
       <c r="G50" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -7525,7 +7525,7 @@
         <v>98</v>
       </c>
       <c r="G51" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -7548,7 +7548,7 @@
         <v>122</v>
       </c>
       <c r="G52" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -7571,7 +7571,7 @@
         <v>126</v>
       </c>
       <c r="G53" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -7594,7 +7594,7 @@
         <v>126</v>
       </c>
       <c r="G54" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -7617,7 +7617,7 @@
         <v>132</v>
       </c>
       <c r="G55" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -7640,7 +7640,7 @@
         <v>136</v>
       </c>
       <c r="G56" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -7663,7 +7663,7 @@
         <v>140</v>
       </c>
       <c r="G57" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -7686,7 +7686,7 @@
         <v>144</v>
       </c>
       <c r="G58" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -7709,7 +7709,7 @@
         <v>144</v>
       </c>
       <c r="G59" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -7732,7 +7732,7 @@
         <v>150</v>
       </c>
       <c r="G60" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -7755,7 +7755,7 @@
         <v>150</v>
       </c>
       <c r="G61" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -7778,7 +7778,7 @@
         <v>156</v>
       </c>
       <c r="G62" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -7801,7 +7801,7 @@
         <v>161</v>
       </c>
       <c r="G63" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -7824,7 +7824,7 @@
         <v>161</v>
       </c>
       <c r="G64" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -7847,7 +7847,7 @@
         <v>161</v>
       </c>
       <c r="G65" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -7870,7 +7870,7 @@
         <v>161</v>
       </c>
       <c r="G66" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -7893,7 +7893,7 @@
         <v>161</v>
       </c>
       <c r="G67" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -7916,7 +7916,7 @@
         <v>161</v>
       </c>
       <c r="G68" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -7939,7 +7939,7 @@
         <v>161</v>
       </c>
       <c r="G69" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -7962,7 +7962,7 @@
         <v>161</v>
       </c>
       <c r="G70" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -7985,7 +7985,7 @@
         <v>161</v>
       </c>
       <c r="G71" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -8008,7 +8008,7 @@
         <v>161</v>
       </c>
       <c r="G72" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -8031,7 +8031,7 @@
         <v>161</v>
       </c>
       <c r="G73" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -8054,7 +8054,7 @@
         <v>185</v>
       </c>
       <c r="G74" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -8077,7 +8077,7 @@
         <v>182</v>
       </c>
       <c r="G75" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -8100,7 +8100,7 @@
         <v>182</v>
       </c>
       <c r="G76" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -8123,7 +8123,7 @@
         <v>182</v>
       </c>
       <c r="G77" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -8146,7 +8146,7 @@
         <v>182</v>
       </c>
       <c r="G78" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -8169,7 +8169,7 @@
         <v>182</v>
       </c>
       <c r="G79" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -8192,7 +8192,7 @@
         <v>182</v>
       </c>
       <c r="G80" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -8215,7 +8215,7 @@
         <v>182</v>
       </c>
       <c r="G81" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -8238,7 +8238,7 @@
         <v>182</v>
       </c>
       <c r="G82" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -8261,7 +8261,7 @@
         <v>182</v>
       </c>
       <c r="G83" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -8284,7 +8284,7 @@
         <v>182</v>
       </c>
       <c r="G84" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -8307,7 +8307,7 @@
         <v>210</v>
       </c>
       <c r="G85" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -8330,7 +8330,7 @@
         <v>210</v>
       </c>
       <c r="G86" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -8353,7 +8353,7 @@
         <v>210</v>
       </c>
       <c r="G87" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -8376,7 +8376,7 @@
         <v>210</v>
       </c>
       <c r="G88" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -8399,7 +8399,7 @@
         <v>210</v>
       </c>
       <c r="G89" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -8422,7 +8422,7 @@
         <v>222</v>
       </c>
       <c r="G90" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -8445,7 +8445,7 @@
         <v>222</v>
       </c>
       <c r="G91" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -8468,7 +8468,7 @@
         <v>222</v>
       </c>
       <c r="G92" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -8491,7 +8491,7 @@
         <v>222</v>
       </c>
       <c r="G93" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -8514,7 +8514,7 @@
         <v>222</v>
       </c>
       <c r="G94" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -8537,7 +8537,7 @@
         <v>234</v>
       </c>
       <c r="G95" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -8545,7 +8545,7 @@
         <v>100091</v>
       </c>
       <c r="B96" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C96" t="s">
         <v>235</v>
@@ -8560,7 +8560,7 @@
         <v>237</v>
       </c>
       <c r="G96" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -8583,7 +8583,7 @@
         <v>237</v>
       </c>
       <c r="G97" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -8606,7 +8606,7 @@
         <v>237</v>
       </c>
       <c r="G98" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -8629,7 +8629,7 @@
         <v>237</v>
       </c>
       <c r="G99" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -8652,7 +8652,7 @@
         <v>237</v>
       </c>
       <c r="G100" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -8675,7 +8675,7 @@
         <v>237</v>
       </c>
       <c r="G101" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -8698,7 +8698,7 @@
         <v>237</v>
       </c>
       <c r="G102" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -8721,7 +8721,7 @@
         <v>253</v>
       </c>
       <c r="G103" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -8744,7 +8744,7 @@
         <v>257</v>
       </c>
       <c r="G104" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -8767,7 +8767,7 @@
         <v>257</v>
       </c>
       <c r="G105" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -8790,7 +8790,7 @@
         <v>145</v>
       </c>
       <c r="G106" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -8813,7 +8813,7 @@
         <v>266</v>
       </c>
       <c r="G107" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -8836,7 +8836,7 @@
         <v>266</v>
       </c>
       <c r="G108" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -8859,7 +8859,7 @@
         <v>266</v>
       </c>
       <c r="G109" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -8882,7 +8882,7 @@
         <v>266</v>
       </c>
       <c r="G110" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -8905,7 +8905,7 @@
         <v>276</v>
       </c>
       <c r="G111" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -8928,7 +8928,7 @@
         <v>276</v>
       </c>
       <c r="G112" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -8951,7 +8951,7 @@
         <v>282</v>
       </c>
       <c r="G113" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -8974,7 +8974,7 @@
         <v>282</v>
       </c>
       <c r="G114" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -8997,7 +8997,7 @@
         <v>282</v>
       </c>
       <c r="G115" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -9020,7 +9020,7 @@
         <v>290</v>
       </c>
       <c r="G116" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -9043,7 +9043,7 @@
         <v>294</v>
       </c>
       <c r="G117" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -9066,7 +9066,7 @@
         <v>294</v>
       </c>
       <c r="G118" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -9089,7 +9089,7 @@
         <v>294</v>
       </c>
       <c r="G119" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -9112,7 +9112,7 @@
         <v>302</v>
       </c>
       <c r="G120" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -9135,7 +9135,7 @@
         <v>276</v>
       </c>
       <c r="G121" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -9158,7 +9158,7 @@
         <v>309</v>
       </c>
       <c r="G122" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -9181,7 +9181,7 @@
         <v>309</v>
       </c>
       <c r="G123" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -9204,7 +9204,7 @@
         <v>309</v>
       </c>
       <c r="G124" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -9227,7 +9227,7 @@
         <v>309</v>
       </c>
       <c r="G125" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -9250,7 +9250,7 @@
         <v>309</v>
       </c>
       <c r="G126" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -9273,7 +9273,7 @@
         <v>309</v>
       </c>
       <c r="G127" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -9296,7 +9296,7 @@
         <v>309</v>
       </c>
       <c r="G128" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -9319,7 +9319,7 @@
         <v>309</v>
       </c>
       <c r="G129" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -9365,7 +9365,7 @@
         <v>309</v>
       </c>
       <c r="G131" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -9388,7 +9388,7 @@
         <v>309</v>
       </c>
       <c r="G132" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -9411,7 +9411,7 @@
         <v>309</v>
       </c>
       <c r="G133" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -9434,7 +9434,7 @@
         <v>309</v>
       </c>
       <c r="G134" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -9457,7 +9457,7 @@
         <v>309</v>
       </c>
       <c r="G135" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -9480,7 +9480,7 @@
         <v>309</v>
       </c>
       <c r="G136" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -9503,7 +9503,7 @@
         <v>309</v>
       </c>
       <c r="G137" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -9526,7 +9526,7 @@
         <v>309</v>
       </c>
       <c r="G138" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -9549,7 +9549,7 @@
         <v>309</v>
       </c>
       <c r="G139" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -9572,7 +9572,7 @@
         <v>309</v>
       </c>
       <c r="G140" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -9595,7 +9595,7 @@
         <v>309</v>
       </c>
       <c r="G141" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -9618,7 +9618,7 @@
         <v>309</v>
       </c>
       <c r="G142" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -9641,7 +9641,7 @@
         <v>309</v>
       </c>
       <c r="G143" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -9664,7 +9664,7 @@
         <v>309</v>
       </c>
       <c r="G144" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -9687,7 +9687,7 @@
         <v>309</v>
       </c>
       <c r="G145" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -9710,7 +9710,7 @@
         <v>309</v>
       </c>
       <c r="G146" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -9733,7 +9733,7 @@
         <v>309</v>
       </c>
       <c r="G147" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -9756,7 +9756,7 @@
         <v>309</v>
       </c>
       <c r="G148" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -9779,7 +9779,7 @@
         <v>309</v>
       </c>
       <c r="G149" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -9802,7 +9802,7 @@
         <v>309</v>
       </c>
       <c r="G150" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -9825,7 +9825,7 @@
         <v>309</v>
       </c>
       <c r="G151" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -9848,7 +9848,7 @@
         <v>309</v>
       </c>
       <c r="G152" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -9871,7 +9871,7 @@
         <v>309</v>
       </c>
       <c r="G153" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -9894,7 +9894,7 @@
         <v>375</v>
       </c>
       <c r="G154" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -9917,7 +9917,7 @@
         <v>126</v>
       </c>
       <c r="G155" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -9940,7 +9940,7 @@
         <v>382</v>
       </c>
       <c r="G156" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -9963,7 +9963,7 @@
         <v>386</v>
       </c>
       <c r="G157" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -9986,7 +9986,7 @@
         <v>390</v>
       </c>
       <c r="G158" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -10009,7 +10009,7 @@
         <v>390</v>
       </c>
       <c r="G159" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -10032,7 +10032,7 @@
         <v>390</v>
       </c>
       <c r="G160" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -10055,7 +10055,7 @@
         <v>398</v>
       </c>
       <c r="G161" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -10078,7 +10078,7 @@
         <v>398</v>
       </c>
       <c r="G162" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -10101,7 +10101,7 @@
         <v>404</v>
       </c>
       <c r="G163" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -10124,7 +10124,7 @@
         <v>404</v>
       </c>
       <c r="G164" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -10147,7 +10147,7 @@
         <v>410</v>
       </c>
       <c r="G165" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -10170,7 +10170,7 @@
         <v>414</v>
       </c>
       <c r="G166" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -10193,7 +10193,7 @@
         <v>418</v>
       </c>
       <c r="G167" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -10216,7 +10216,7 @@
         <v>418</v>
       </c>
       <c r="G168" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -10239,7 +10239,7 @@
         <v>418</v>
       </c>
       <c r="G169" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -10262,7 +10262,7 @@
         <v>418</v>
       </c>
       <c r="G170" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -10285,7 +10285,7 @@
         <v>418</v>
       </c>
       <c r="G171" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -10308,7 +10308,7 @@
         <v>418</v>
       </c>
       <c r="G172" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -10331,7 +10331,7 @@
         <v>418</v>
       </c>
       <c r="G173" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -10354,7 +10354,7 @@
         <v>434</v>
       </c>
       <c r="G174" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -10377,7 +10377,7 @@
         <v>434</v>
       </c>
       <c r="G175" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -10400,7 +10400,7 @@
         <v>434</v>
       </c>
       <c r="G176" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -10423,7 +10423,7 @@
         <v>434</v>
       </c>
       <c r="G177" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -10446,7 +10446,7 @@
         <v>444</v>
       </c>
       <c r="G178" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -10469,7 +10469,7 @@
         <v>444</v>
       </c>
       <c r="G179" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -10492,7 +10492,7 @@
         <v>444</v>
       </c>
       <c r="G180" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -10515,7 +10515,7 @@
         <v>444</v>
       </c>
       <c r="G181" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -10538,7 +10538,7 @@
         <v>444</v>
       </c>
       <c r="G182" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -10561,7 +10561,7 @@
         <v>456</v>
       </c>
       <c r="G183" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -10584,7 +10584,7 @@
         <v>460</v>
       </c>
       <c r="G184" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -10607,7 +10607,7 @@
         <v>460</v>
       </c>
       <c r="G185" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -10630,7 +10630,7 @@
         <v>460</v>
       </c>
       <c r="G186" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -10653,7 +10653,7 @@
         <v>460</v>
       </c>
       <c r="G187" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -10676,7 +10676,7 @@
         <v>460</v>
       </c>
       <c r="G188" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -10699,7 +10699,7 @@
         <v>460</v>
       </c>
       <c r="G189" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -10722,7 +10722,7 @@
         <v>460</v>
       </c>
       <c r="G190" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
@@ -10745,7 +10745,7 @@
         <v>460</v>
       </c>
       <c r="G191" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
@@ -10768,7 +10768,7 @@
         <v>478</v>
       </c>
       <c r="G192" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
@@ -10791,7 +10791,7 @@
         <v>197</v>
       </c>
       <c r="G193" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -10814,7 +10814,7 @@
         <v>197</v>
       </c>
       <c r="G194" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
@@ -10860,7 +10860,7 @@
         <v>197</v>
       </c>
       <c r="G196" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -10883,7 +10883,7 @@
         <v>197</v>
       </c>
       <c r="G197" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
@@ -10906,7 +10906,7 @@
         <v>197</v>
       </c>
       <c r="G198" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -10929,7 +10929,7 @@
         <v>197</v>
       </c>
       <c r="G199" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
@@ -10952,7 +10952,7 @@
         <v>197</v>
       </c>
       <c r="G200" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -10975,7 +10975,7 @@
         <v>197</v>
       </c>
       <c r="G201" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
@@ -10998,7 +10998,7 @@
         <v>197</v>
       </c>
       <c r="G202" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
@@ -11021,7 +11021,7 @@
         <v>197</v>
       </c>
       <c r="G203" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
@@ -11044,7 +11044,7 @@
         <v>197</v>
       </c>
       <c r="G204" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
@@ -11067,7 +11067,7 @@
         <v>197</v>
       </c>
       <c r="G205" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
@@ -11090,7 +11090,7 @@
         <v>509</v>
       </c>
       <c r="G206" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
@@ -11113,7 +11113,7 @@
         <v>509</v>
       </c>
       <c r="G207" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
@@ -11136,7 +11136,7 @@
         <v>515</v>
       </c>
       <c r="G208" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
@@ -11159,7 +11159,7 @@
         <v>515</v>
       </c>
       <c r="G209" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
@@ -11182,7 +11182,7 @@
         <v>515</v>
       </c>
       <c r="G210" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
@@ -11205,7 +11205,7 @@
         <v>515</v>
       </c>
       <c r="G211" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
@@ -11228,7 +11228,7 @@
         <v>515</v>
       </c>
       <c r="G212" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
@@ -11251,7 +11251,7 @@
         <v>515</v>
       </c>
       <c r="G213" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
@@ -11274,7 +11274,7 @@
         <v>515</v>
       </c>
       <c r="G214" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
@@ -11297,7 +11297,7 @@
         <v>531</v>
       </c>
       <c r="G215" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
@@ -11320,7 +11320,7 @@
         <v>531</v>
       </c>
       <c r="G216" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
@@ -11343,7 +11343,7 @@
         <v>531</v>
       </c>
       <c r="G217" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
@@ -11366,7 +11366,7 @@
         <v>531</v>
       </c>
       <c r="G218" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
@@ -11389,7 +11389,7 @@
         <v>531</v>
       </c>
       <c r="G219" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
@@ -11412,7 +11412,7 @@
         <v>531</v>
       </c>
       <c r="G220" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
@@ -11435,7 +11435,7 @@
         <v>531</v>
       </c>
       <c r="G221" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
@@ -11458,7 +11458,7 @@
         <v>531</v>
       </c>
       <c r="G222" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
@@ -11481,7 +11481,7 @@
         <v>531</v>
       </c>
       <c r="G223" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
@@ -11527,7 +11527,7 @@
         <v>553</v>
       </c>
       <c r="G225" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
@@ -11550,7 +11550,7 @@
         <v>553</v>
       </c>
       <c r="G226" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
@@ -11573,7 +11573,7 @@
         <v>559</v>
       </c>
       <c r="G227" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
@@ -11596,7 +11596,7 @@
         <v>563</v>
       </c>
       <c r="G228" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
@@ -11619,7 +11619,7 @@
         <v>563</v>
       </c>
       <c r="G229" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
@@ -11642,7 +11642,7 @@
         <v>563</v>
       </c>
       <c r="G230" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
@@ -11665,7 +11665,7 @@
         <v>563</v>
       </c>
       <c r="G231" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
@@ -11688,7 +11688,7 @@
         <v>563</v>
       </c>
       <c r="G232" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
@@ -11711,7 +11711,7 @@
         <v>563</v>
       </c>
       <c r="G233" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
@@ -11734,7 +11734,7 @@
         <v>563</v>
       </c>
       <c r="G234" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -11757,7 +11757,7 @@
         <v>563</v>
       </c>
       <c r="G235" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
@@ -11780,7 +11780,7 @@
         <v>563</v>
       </c>
       <c r="G236" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
@@ -11803,7 +11803,7 @@
         <v>563</v>
       </c>
       <c r="G237" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
@@ -11826,7 +11826,7 @@
         <v>563</v>
       </c>
       <c r="G238" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
@@ -11849,7 +11849,7 @@
         <v>563</v>
       </c>
       <c r="G239" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
@@ -11872,7 +11872,7 @@
         <v>563</v>
       </c>
       <c r="G240" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
@@ -11895,7 +11895,7 @@
         <v>563</v>
       </c>
       <c r="G241" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
@@ -11918,7 +11918,7 @@
         <v>563</v>
       </c>
       <c r="G242" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
@@ -11941,7 +11941,7 @@
         <v>595</v>
       </c>
       <c r="G243" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
@@ -11964,7 +11964,7 @@
         <v>595</v>
       </c>
       <c r="G244" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
@@ -11987,7 +11987,7 @@
         <v>595</v>
       </c>
       <c r="G245" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
@@ -12010,7 +12010,7 @@
         <v>595</v>
       </c>
       <c r="G246" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
@@ -12033,7 +12033,7 @@
         <v>595</v>
       </c>
       <c r="G247" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
@@ -12056,7 +12056,7 @@
         <v>595</v>
       </c>
       <c r="G248" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
@@ -12079,7 +12079,7 @@
         <v>609</v>
       </c>
       <c r="G249" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
@@ -12102,7 +12102,7 @@
         <v>613</v>
       </c>
       <c r="G250" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
@@ -12125,7 +12125,7 @@
         <v>617</v>
       </c>
       <c r="G251" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
@@ -12148,7 +12148,7 @@
         <v>617</v>
       </c>
       <c r="G252" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
@@ -12171,7 +12171,7 @@
         <v>617</v>
       </c>
       <c r="G253" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
@@ -12194,7 +12194,7 @@
         <v>617</v>
       </c>
       <c r="G254" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
@@ -12217,7 +12217,7 @@
         <v>617</v>
       </c>
       <c r="G255" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
@@ -12240,7 +12240,7 @@
         <v>617</v>
       </c>
       <c r="G256" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
@@ -12263,7 +12263,7 @@
         <v>617</v>
       </c>
       <c r="G257" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
@@ -12286,7 +12286,7 @@
         <v>617</v>
       </c>
       <c r="G258" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
@@ -12309,7 +12309,7 @@
         <v>617</v>
       </c>
       <c r="G259" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
@@ -12332,7 +12332,7 @@
         <v>617</v>
       </c>
       <c r="G260" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
@@ -12355,7 +12355,7 @@
         <v>617</v>
       </c>
       <c r="G261" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
@@ -12378,7 +12378,7 @@
         <v>617</v>
       </c>
       <c r="G262" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
@@ -12401,7 +12401,7 @@
         <v>617</v>
       </c>
       <c r="G263" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
@@ -12424,7 +12424,7 @@
         <v>617</v>
       </c>
       <c r="G264" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
@@ -12447,7 +12447,7 @@
         <v>647</v>
       </c>
       <c r="G265" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
@@ -12470,7 +12470,7 @@
         <v>651</v>
       </c>
       <c r="G266" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
@@ -12493,7 +12493,7 @@
         <v>655</v>
       </c>
       <c r="G267" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
@@ -12516,7 +12516,7 @@
         <v>655</v>
       </c>
       <c r="G268" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
@@ -12539,7 +12539,7 @@
         <v>661</v>
       </c>
       <c r="G269" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
@@ -12562,7 +12562,7 @@
         <v>661</v>
       </c>
       <c r="G270" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
@@ -12585,7 +12585,7 @@
         <v>661</v>
       </c>
       <c r="G271" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
@@ -12608,7 +12608,7 @@
         <v>661</v>
       </c>
       <c r="G272" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
@@ -12631,7 +12631,7 @@
         <v>661</v>
       </c>
       <c r="G273" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
@@ -12654,7 +12654,7 @@
         <v>661</v>
       </c>
       <c r="G274" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
@@ -12677,7 +12677,7 @@
         <v>675</v>
       </c>
       <c r="G275" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
@@ -12700,7 +12700,7 @@
         <v>675</v>
       </c>
       <c r="G276" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
@@ -12723,7 +12723,7 @@
         <v>675</v>
       </c>
       <c r="G277" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
@@ -12746,7 +12746,7 @@
         <v>675</v>
       </c>
       <c r="G278" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
@@ -12769,7 +12769,7 @@
         <v>675</v>
       </c>
       <c r="G279" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
@@ -12792,7 +12792,7 @@
         <v>687</v>
       </c>
       <c r="G280" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
@@ -12815,7 +12815,7 @@
         <v>687</v>
       </c>
       <c r="G281" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
@@ -12838,7 +12838,7 @@
         <v>687</v>
       </c>
       <c r="G282" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
@@ -12861,7 +12861,7 @@
         <v>687</v>
       </c>
       <c r="G283" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
@@ -12884,7 +12884,7 @@
         <v>687</v>
       </c>
       <c r="G284" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
@@ -12907,7 +12907,7 @@
         <v>699</v>
       </c>
       <c r="G285" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
@@ -12930,7 +12930,7 @@
         <v>703</v>
       </c>
       <c r="G286" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
@@ -12953,7 +12953,7 @@
         <v>707</v>
       </c>
       <c r="G287" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.25">
@@ -12976,7 +12976,7 @@
         <v>711</v>
       </c>
       <c r="G288" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
@@ -12999,7 +12999,7 @@
         <v>715</v>
       </c>
       <c r="G289" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
@@ -13022,7 +13022,7 @@
         <v>719</v>
       </c>
       <c r="G290" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
@@ -13045,7 +13045,7 @@
         <v>556</v>
       </c>
       <c r="G291" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
@@ -13068,7 +13068,7 @@
         <v>556</v>
       </c>
       <c r="G292" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
@@ -13091,7 +13091,7 @@
         <v>556</v>
       </c>
       <c r="G293" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.25">
@@ -13114,7 +13114,7 @@
         <v>556</v>
       </c>
       <c r="G294" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
@@ -13137,7 +13137,7 @@
         <v>556</v>
       </c>
       <c r="G295" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
@@ -13160,7 +13160,7 @@
         <v>556</v>
       </c>
       <c r="G296" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
@@ -13183,7 +13183,7 @@
         <v>737</v>
       </c>
       <c r="G297" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
@@ -13206,7 +13206,7 @@
         <v>737</v>
       </c>
       <c r="G298" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.25">
@@ -13229,7 +13229,7 @@
         <v>737</v>
       </c>
       <c r="G299" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.25">
@@ -13252,7 +13252,7 @@
         <v>737</v>
       </c>
       <c r="G300" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.25">
@@ -13275,7 +13275,7 @@
         <v>737</v>
       </c>
       <c r="G301" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.25">
@@ -13298,7 +13298,7 @@
         <v>747</v>
       </c>
       <c r="G302" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.25">
@@ -13321,7 +13321,7 @@
         <v>747</v>
       </c>
       <c r="G303" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.25">
@@ -13344,7 +13344,7 @@
         <v>747</v>
       </c>
       <c r="G304" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.25">
@@ -13367,7 +13367,7 @@
         <v>755</v>
       </c>
       <c r="G305" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.25">
@@ -13390,7 +13390,7 @@
         <v>755</v>
       </c>
       <c r="G306" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.25">
@@ -13413,7 +13413,7 @@
         <v>755</v>
       </c>
       <c r="G307" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.25">
@@ -13436,7 +13436,7 @@
         <v>755</v>
       </c>
       <c r="G308" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.25">
@@ -13459,7 +13459,7 @@
         <v>765</v>
       </c>
       <c r="G309" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.25">
@@ -13505,7 +13505,7 @@
         <v>765</v>
       </c>
       <c r="G311" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.25">
@@ -13528,7 +13528,7 @@
         <v>765</v>
       </c>
       <c r="G312" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.25">
@@ -13551,7 +13551,7 @@
         <v>775</v>
       </c>
       <c r="G313" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.25">
@@ -13574,7 +13574,7 @@
         <v>775</v>
       </c>
       <c r="G314" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.25">
@@ -13597,7 +13597,7 @@
         <v>781</v>
       </c>
       <c r="G315" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">
@@ -13620,7 +13620,7 @@
         <v>781</v>
       </c>
       <c r="G316" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.25">
@@ -13643,7 +13643,7 @@
         <v>787</v>
       </c>
       <c r="G317" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.25">
@@ -13666,7 +13666,7 @@
         <v>790</v>
       </c>
       <c r="G318" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.25">
@@ -13689,7 +13689,7 @@
         <v>794</v>
       </c>
       <c r="G319" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.25">
@@ -13712,7 +13712,7 @@
         <v>794</v>
       </c>
       <c r="G320" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.25">
@@ -13735,7 +13735,7 @@
         <v>794</v>
       </c>
       <c r="G321" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.25">
@@ -13758,7 +13758,7 @@
         <v>801</v>
       </c>
       <c r="G322" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.25">
@@ -13781,7 +13781,7 @@
         <v>801</v>
       </c>
       <c r="G323" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.25">
@@ -13804,7 +13804,7 @@
         <v>801</v>
       </c>
       <c r="G324" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.25">
@@ -13827,7 +13827,7 @@
         <v>801</v>
       </c>
       <c r="G325" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.25">
@@ -13850,7 +13850,7 @@
         <v>801</v>
       </c>
       <c r="G326" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.25">
@@ -13873,7 +13873,7 @@
         <v>813</v>
       </c>
       <c r="G327" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.25">
@@ -13896,7 +13896,7 @@
         <v>817</v>
       </c>
       <c r="G328" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.25">
@@ -13919,7 +13919,7 @@
         <v>821</v>
       </c>
       <c r="G329" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.25">
@@ -13942,7 +13942,7 @@
         <v>821</v>
       </c>
       <c r="G330" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.25">
@@ -13965,7 +13965,7 @@
         <v>827</v>
       </c>
       <c r="G331" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.25">
@@ -13988,7 +13988,7 @@
         <v>366</v>
       </c>
       <c r="G332" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.25">
@@ -14011,7 +14011,7 @@
         <v>833</v>
       </c>
       <c r="G333" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.25">
@@ -14034,7 +14034,7 @@
         <v>833</v>
       </c>
       <c r="G334" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.25">
@@ -14057,7 +14057,7 @@
         <v>833</v>
       </c>
       <c r="G335" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.25">
@@ -14080,7 +14080,7 @@
         <v>841</v>
       </c>
       <c r="G336" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.25">
@@ -14103,7 +14103,7 @@
         <v>841</v>
       </c>
       <c r="G337" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.25">
@@ -14126,7 +14126,7 @@
         <v>841</v>
       </c>
       <c r="G338" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.25">
@@ -14149,7 +14149,7 @@
         <v>841</v>
       </c>
       <c r="G339" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.25">
@@ -14172,7 +14172,7 @@
         <v>841</v>
       </c>
       <c r="G340" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.25">
@@ -14195,7 +14195,7 @@
         <v>841</v>
       </c>
       <c r="G341" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.25">
@@ -14218,7 +14218,7 @@
         <v>855</v>
       </c>
       <c r="G342" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.25">
@@ -14241,7 +14241,7 @@
         <v>859</v>
       </c>
       <c r="G343" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.25">
@@ -14264,7 +14264,7 @@
         <v>506</v>
       </c>
       <c r="G344" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.25">
@@ -14287,7 +14287,7 @@
         <v>399</v>
       </c>
       <c r="G345" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.25">
@@ -14310,7 +14310,7 @@
         <v>399</v>
       </c>
       <c r="G346" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.25">
@@ -14333,7 +14333,7 @@
         <v>399</v>
       </c>
       <c r="G347" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.25">
@@ -14356,7 +14356,7 @@
         <v>399</v>
       </c>
       <c r="G348" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.25">
@@ -14379,7 +14379,7 @@
         <v>399</v>
       </c>
       <c r="G349" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.25">
@@ -14402,7 +14402,7 @@
         <v>399</v>
       </c>
       <c r="G350" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.25">
@@ -14425,7 +14425,7 @@
         <v>699</v>
       </c>
       <c r="G351" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.25">
@@ -14448,7 +14448,7 @@
         <v>880</v>
       </c>
       <c r="G352" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.25">
@@ -14471,7 +14471,7 @@
         <v>880</v>
       </c>
       <c r="G353" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.25">
@@ -14494,7 +14494,7 @@
         <v>880</v>
       </c>
       <c r="G354" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.25">
@@ -14517,7 +14517,7 @@
         <v>880</v>
       </c>
       <c r="G355" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.25">
@@ -14540,7 +14540,7 @@
         <v>880</v>
       </c>
       <c r="G356" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.25">
@@ -14563,7 +14563,7 @@
         <v>891</v>
       </c>
       <c r="G357" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.25">
@@ -14586,7 +14586,7 @@
         <v>891</v>
       </c>
       <c r="G358" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.25">
@@ -14609,7 +14609,7 @@
         <v>897</v>
       </c>
       <c r="G359" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.25">
@@ -14632,7 +14632,7 @@
         <v>897</v>
       </c>
       <c r="G360" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.25">
@@ -14655,7 +14655,7 @@
         <v>434</v>
       </c>
       <c r="G361" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.25">
@@ -14678,7 +14678,7 @@
         <v>434</v>
       </c>
       <c r="G362" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.25">
@@ -14701,7 +14701,7 @@
         <v>908</v>
       </c>
       <c r="G363" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.25">
@@ -14724,7 +14724,7 @@
         <v>908</v>
       </c>
       <c r="G364" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.25">
@@ -14747,7 +14747,7 @@
         <v>488</v>
       </c>
       <c r="G365" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.25">
@@ -14770,7 +14770,7 @@
         <v>488</v>
       </c>
       <c r="G366" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.25">
@@ -14793,7 +14793,7 @@
         <v>919</v>
       </c>
       <c r="G367" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.25">
@@ -14816,7 +14816,7 @@
         <v>923</v>
       </c>
       <c r="G368" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.25">
@@ -14839,7 +14839,7 @@
         <v>927</v>
       </c>
       <c r="G369" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.25">
@@ -14862,7 +14862,7 @@
         <v>928</v>
       </c>
       <c r="G370" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.25">
@@ -14885,7 +14885,7 @@
         <v>928</v>
       </c>
       <c r="G371" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.25">
@@ -14908,7 +14908,7 @@
         <v>937</v>
       </c>
       <c r="G372" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.25">
@@ -14931,7 +14931,7 @@
         <v>941</v>
       </c>
       <c r="G373" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.25">
@@ -14954,7 +14954,7 @@
         <v>941</v>
       </c>
       <c r="G374" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.25">
@@ -14977,7 +14977,7 @@
         <v>941</v>
       </c>
       <c r="G375" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.25">
@@ -15000,7 +15000,7 @@
         <v>949</v>
       </c>
       <c r="G376" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.25">
@@ -15023,7 +15023,7 @@
         <v>949</v>
       </c>
       <c r="G377" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.25">
@@ -15046,7 +15046,7 @@
         <v>949</v>
       </c>
       <c r="G378" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.25">
@@ -15069,7 +15069,7 @@
         <v>949</v>
       </c>
       <c r="G379" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.25">
@@ -15092,7 +15092,7 @@
         <v>949</v>
       </c>
       <c r="G380" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.25">
@@ -15115,7 +15115,7 @@
         <v>949</v>
       </c>
       <c r="G381" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.25">
@@ -15138,7 +15138,7 @@
         <v>949</v>
       </c>
       <c r="G382" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.25">
@@ -15161,7 +15161,7 @@
         <v>949</v>
       </c>
       <c r="G383" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.25">
@@ -15184,7 +15184,7 @@
         <v>965</v>
       </c>
       <c r="G384" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.25">
@@ -15207,7 +15207,7 @@
         <v>969</v>
       </c>
       <c r="G385" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.25">
@@ -15230,7 +15230,7 @@
         <v>969</v>
       </c>
       <c r="G386" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.25">
@@ -15253,7 +15253,7 @@
         <v>969</v>
       </c>
       <c r="G387" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.25">
@@ -15276,7 +15276,7 @@
         <v>969</v>
       </c>
       <c r="G388" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.25">
@@ -15299,7 +15299,7 @@
         <v>969</v>
       </c>
       <c r="G389" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.25">
@@ -15322,7 +15322,7 @@
         <v>969</v>
       </c>
       <c r="G390" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.25">
@@ -15345,7 +15345,7 @@
         <v>981</v>
       </c>
       <c r="G391" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.25">
@@ -15368,7 +15368,7 @@
         <v>985</v>
       </c>
       <c r="G392" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.25">
@@ -15391,7 +15391,7 @@
         <v>985</v>
       </c>
       <c r="G393" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.25">
@@ -15414,7 +15414,7 @@
         <v>991</v>
       </c>
       <c r="G394" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.25">
@@ -15437,7 +15437,7 @@
         <v>995</v>
       </c>
       <c r="G395" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.25">
@@ -15460,7 +15460,7 @@
         <v>999</v>
       </c>
       <c r="G396" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.25">
@@ -15483,7 +15483,7 @@
         <v>737</v>
       </c>
       <c r="G397" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.25">
@@ -15506,7 +15506,7 @@
         <v>1006</v>
       </c>
       <c r="G398" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.25">
@@ -15529,7 +15529,7 @@
         <v>1010</v>
       </c>
       <c r="G399" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.25">
@@ -15552,7 +15552,7 @@
         <v>1013</v>
       </c>
       <c r="G400" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.25">
@@ -15575,7 +15575,7 @@
         <v>1013</v>
       </c>
       <c r="G401" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.25">
@@ -15598,7 +15598,7 @@
         <v>1013</v>
       </c>
       <c r="G402" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.25">
@@ -15621,7 +15621,7 @@
         <v>1013</v>
       </c>
       <c r="G403" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.25">
@@ -15644,7 +15644,7 @@
         <v>1013</v>
       </c>
       <c r="G404" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.25">
@@ -15667,7 +15667,7 @@
         <v>1013</v>
       </c>
       <c r="G405" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.25">
@@ -15690,7 +15690,7 @@
         <v>747</v>
       </c>
       <c r="G406" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.25">
@@ -15713,7 +15713,7 @@
         <v>1028</v>
       </c>
       <c r="G407" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.25">
@@ -15736,7 +15736,7 @@
         <v>1032</v>
       </c>
       <c r="G408" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.25">
@@ -15759,7 +15759,7 @@
         <v>1036</v>
       </c>
       <c r="G409" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.25">
@@ -15782,7 +15782,7 @@
         <v>1036</v>
       </c>
       <c r="G410" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.25">
@@ -15805,7 +15805,7 @@
         <v>1036</v>
       </c>
       <c r="G411" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.25">
@@ -15828,7 +15828,7 @@
         <v>1044</v>
       </c>
       <c r="G412" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="413" spans="1:7" x14ac:dyDescent="0.25">
@@ -15851,7 +15851,7 @@
         <v>1049</v>
       </c>
       <c r="G413" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="414" spans="1:7" x14ac:dyDescent="0.25">
@@ -15874,7 +15874,7 @@
         <v>1049</v>
       </c>
       <c r="G414" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="415" spans="1:7" x14ac:dyDescent="0.25">
@@ -15897,7 +15897,7 @@
         <v>1049</v>
       </c>
       <c r="G415" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.25">
@@ -15920,7 +15920,7 @@
         <v>1049</v>
       </c>
       <c r="G416" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.25">
@@ -15943,7 +15943,7 @@
         <v>1049</v>
       </c>
       <c r="G417" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.25">
@@ -15966,7 +15966,7 @@
         <v>1049</v>
       </c>
       <c r="G418" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.25">
@@ -15989,7 +15989,7 @@
         <v>1049</v>
       </c>
       <c r="G419" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.25">
@@ -16012,7 +16012,7 @@
         <v>1049</v>
       </c>
       <c r="G420" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.25">
@@ -16035,7 +16035,7 @@
         <v>1049</v>
       </c>
       <c r="G421" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.25">
@@ -16058,7 +16058,7 @@
         <v>1049</v>
       </c>
       <c r="G422" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.25">
@@ -16081,7 +16081,7 @@
         <v>1070</v>
       </c>
       <c r="G423" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.25">
@@ -16104,7 +16104,7 @@
         <v>1070</v>
       </c>
       <c r="G424" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.25">
@@ -16127,7 +16127,7 @@
         <v>1076</v>
       </c>
       <c r="G425" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.25">
@@ -16150,7 +16150,7 @@
         <v>1080</v>
       </c>
       <c r="G426" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.25">
@@ -16173,7 +16173,7 @@
         <v>1080</v>
       </c>
       <c r="G427" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.25">
@@ -16219,7 +16219,7 @@
         <v>1080</v>
       </c>
       <c r="G429" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.25">
@@ -16242,7 +16242,7 @@
         <v>1080</v>
       </c>
       <c r="G430" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.25">
@@ -16265,7 +16265,7 @@
         <v>1080</v>
       </c>
       <c r="G431" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.25">
@@ -16288,7 +16288,7 @@
         <v>1080</v>
       </c>
       <c r="G432" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.25">
@@ -16311,7 +16311,7 @@
         <v>1080</v>
       </c>
       <c r="G433" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.25">
@@ -16334,7 +16334,7 @@
         <v>1080</v>
       </c>
       <c r="G434" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.25">
@@ -16357,7 +16357,7 @@
         <v>1096</v>
       </c>
       <c r="G435" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.25">
@@ -16380,7 +16380,7 @@
         <v>1100</v>
       </c>
       <c r="G436" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.25">
@@ -16403,7 +16403,7 @@
         <v>1100</v>
       </c>
       <c r="G437" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.25">
@@ -16426,7 +16426,7 @@
         <v>1100</v>
       </c>
       <c r="G438" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.25">
@@ -16449,7 +16449,7 @@
         <v>1100</v>
       </c>
       <c r="G439" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.25">
@@ -16472,7 +16472,7 @@
         <v>1100</v>
       </c>
       <c r="G440" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.25">
@@ -16495,7 +16495,7 @@
         <v>1110</v>
       </c>
       <c r="G441" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.25">
@@ -16518,7 +16518,7 @@
         <v>1114</v>
       </c>
       <c r="G442" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.25">
@@ -16541,7 +16541,7 @@
         <v>1114</v>
       </c>
       <c r="G443" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.25">
@@ -16564,7 +16564,7 @@
         <v>1120</v>
       </c>
       <c r="G444" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.25">
@@ -16587,7 +16587,7 @@
         <v>1120</v>
       </c>
       <c r="G445" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.25">
@@ -16610,7 +16610,7 @@
         <v>1120</v>
       </c>
       <c r="G446" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.25">
@@ -16633,7 +16633,7 @@
         <v>1120</v>
       </c>
       <c r="G447" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.25">
@@ -16656,7 +16656,7 @@
         <v>1120</v>
       </c>
       <c r="G448" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.25">
@@ -16679,7 +16679,7 @@
         <v>1120</v>
       </c>
       <c r="G449" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="450" spans="1:7" x14ac:dyDescent="0.25">
@@ -16702,7 +16702,7 @@
         <v>1120</v>
       </c>
       <c r="G450" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.25">
@@ -16725,7 +16725,7 @@
         <v>1120</v>
       </c>
       <c r="G451" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="452" spans="1:7" x14ac:dyDescent="0.25">
@@ -16748,7 +16748,7 @@
         <v>791</v>
       </c>
       <c r="G452" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="453" spans="1:7" x14ac:dyDescent="0.25">
@@ -16771,7 +16771,7 @@
         <v>1141</v>
       </c>
       <c r="G453" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.25">
@@ -16794,7 +16794,7 @@
         <v>1145</v>
       </c>
       <c r="G454" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="455" spans="1:7" x14ac:dyDescent="0.25">
@@ -16817,7 +16817,7 @@
         <v>1148</v>
       </c>
       <c r="G455" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="456" spans="1:7" x14ac:dyDescent="0.25">
@@ -16840,7 +16840,7 @@
         <v>1152</v>
       </c>
       <c r="G456" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="457" spans="1:7" x14ac:dyDescent="0.25">
@@ -16863,7 +16863,7 @@
         <v>1156</v>
       </c>
       <c r="G457" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="458" spans="1:7" x14ac:dyDescent="0.25">
@@ -16886,7 +16886,7 @@
         <v>1156</v>
       </c>
       <c r="G458" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.25">
@@ -16909,7 +16909,7 @@
         <v>1162</v>
       </c>
       <c r="G459" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="460" spans="1:7" x14ac:dyDescent="0.25">
@@ -16932,7 +16932,7 @@
         <v>1166</v>
       </c>
       <c r="G460" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="461" spans="1:7" x14ac:dyDescent="0.25">
@@ -16955,7 +16955,7 @@
         <v>1166</v>
       </c>
       <c r="G461" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="462" spans="1:7" x14ac:dyDescent="0.25">
@@ -16978,7 +16978,7 @@
         <v>1166</v>
       </c>
       <c r="G462" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="463" spans="1:7" x14ac:dyDescent="0.25">
@@ -17001,7 +17001,7 @@
         <v>1166</v>
       </c>
       <c r="G463" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="464" spans="1:7" x14ac:dyDescent="0.25">
@@ -17024,7 +17024,7 @@
         <v>1166</v>
       </c>
       <c r="G464" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="465" spans="1:7" x14ac:dyDescent="0.25">
@@ -17047,7 +17047,7 @@
         <v>1177</v>
       </c>
       <c r="G465" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="466" spans="1:7" x14ac:dyDescent="0.25">
@@ -17070,7 +17070,7 @@
         <v>1181</v>
       </c>
       <c r="G466" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="467" spans="1:7" x14ac:dyDescent="0.25">
@@ -17093,7 +17093,7 @@
         <v>1185</v>
       </c>
       <c r="G467" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="468" spans="1:7" x14ac:dyDescent="0.25">
@@ -17116,7 +17116,7 @@
         <v>1185</v>
       </c>
       <c r="G468" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="469" spans="1:7" x14ac:dyDescent="0.25">
@@ -17139,7 +17139,7 @@
         <v>1185</v>
       </c>
       <c r="G469" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="470" spans="1:7" x14ac:dyDescent="0.25">
@@ -17162,7 +17162,7 @@
         <v>368</v>
       </c>
       <c r="G470" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="471" spans="1:7" x14ac:dyDescent="0.25">
@@ -17185,7 +17185,7 @@
         <v>1194</v>
       </c>
       <c r="G471" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="472" spans="1:7" x14ac:dyDescent="0.25">
@@ -17208,7 +17208,7 @@
         <v>1198</v>
       </c>
       <c r="G472" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="473" spans="1:7" x14ac:dyDescent="0.25">
@@ -17254,7 +17254,7 @@
         <v>1202</v>
       </c>
       <c r="G474" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="475" spans="1:7" x14ac:dyDescent="0.25">
@@ -17277,7 +17277,7 @@
         <v>841</v>
       </c>
       <c r="G475" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="476" spans="1:7" x14ac:dyDescent="0.25">
@@ -17300,7 +17300,7 @@
         <v>841</v>
       </c>
       <c r="G476" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="477" spans="1:7" x14ac:dyDescent="0.25">
@@ -17323,7 +17323,7 @@
         <v>841</v>
       </c>
       <c r="G477" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="478" spans="1:7" x14ac:dyDescent="0.25">
@@ -17346,7 +17346,7 @@
         <v>841</v>
       </c>
       <c r="G478" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="479" spans="1:7" x14ac:dyDescent="0.25">
@@ -17369,7 +17369,7 @@
         <v>841</v>
       </c>
       <c r="G479" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="480" spans="1:7" x14ac:dyDescent="0.25">
@@ -17392,7 +17392,7 @@
         <v>841</v>
       </c>
       <c r="G480" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="481" spans="1:7" x14ac:dyDescent="0.25">
@@ -17415,7 +17415,7 @@
         <v>841</v>
       </c>
       <c r="G481" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="482" spans="1:7" x14ac:dyDescent="0.25">
@@ -17438,7 +17438,7 @@
         <v>841</v>
       </c>
       <c r="G482" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="483" spans="1:7" x14ac:dyDescent="0.25">
@@ -17461,7 +17461,7 @@
         <v>841</v>
       </c>
       <c r="G483" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="484" spans="1:7" x14ac:dyDescent="0.25">
@@ -17484,7 +17484,7 @@
         <v>841</v>
       </c>
       <c r="G484" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="485" spans="1:7" x14ac:dyDescent="0.25">
@@ -17507,7 +17507,7 @@
         <v>841</v>
       </c>
       <c r="G485" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="486" spans="1:7" x14ac:dyDescent="0.25">
@@ -17530,7 +17530,7 @@
         <v>841</v>
       </c>
       <c r="G486" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="487" spans="1:7" x14ac:dyDescent="0.25">
@@ -17553,7 +17553,7 @@
         <v>841</v>
       </c>
       <c r="G487" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="488" spans="1:7" x14ac:dyDescent="0.25">
@@ -17576,7 +17576,7 @@
         <v>841</v>
       </c>
       <c r="G488" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.25">
@@ -17599,7 +17599,7 @@
         <v>841</v>
       </c>
       <c r="G489" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="490" spans="1:7" x14ac:dyDescent="0.25">
@@ -17622,7 +17622,7 @@
         <v>841</v>
       </c>
       <c r="G490" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.25">
@@ -17645,7 +17645,7 @@
         <v>841</v>
       </c>
       <c r="G491" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.25">
@@ -17668,7 +17668,7 @@
         <v>841</v>
       </c>
       <c r="G492" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.25">
@@ -17691,7 +17691,7 @@
         <v>841</v>
       </c>
       <c r="G493" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.25">
@@ -17714,7 +17714,7 @@
         <v>841</v>
       </c>
       <c r="G494" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.25">
@@ -17737,7 +17737,7 @@
         <v>841</v>
       </c>
       <c r="G495" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.25">
@@ -17760,7 +17760,7 @@
         <v>841</v>
       </c>
       <c r="G496" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.25">
@@ -17806,7 +17806,7 @@
         <v>841</v>
       </c>
       <c r="G498" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.25">
@@ -17829,7 +17829,7 @@
         <v>1255</v>
       </c>
       <c r="G499" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.25">
@@ -17852,7 +17852,7 @@
         <v>1259</v>
       </c>
       <c r="G500" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.25">
@@ -17875,7 +17875,7 @@
         <v>1262</v>
       </c>
       <c r="G501" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.25">
@@ -17898,7 +17898,7 @@
         <v>1266</v>
       </c>
       <c r="G502" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.25">
@@ -17921,7 +17921,7 @@
         <v>1266</v>
       </c>
       <c r="G503" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.25">
@@ -17944,7 +17944,7 @@
         <v>157</v>
       </c>
       <c r="G504" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.25">
@@ -17967,7 +17967,7 @@
         <v>1274</v>
       </c>
       <c r="G505" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="506" spans="1:7" x14ac:dyDescent="0.25">
@@ -17990,7 +17990,7 @@
         <v>1274</v>
       </c>
       <c r="G506" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.25">
@@ -18013,7 +18013,7 @@
         <v>1280</v>
       </c>
       <c r="G507" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.25">
@@ -18036,7 +18036,7 @@
         <v>1280</v>
       </c>
       <c r="G508" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.25">
@@ -18059,7 +18059,7 @@
         <v>1280</v>
       </c>
       <c r="G509" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.25">
@@ -18082,7 +18082,7 @@
         <v>1280</v>
       </c>
       <c r="G510" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.25">
@@ -18090,7 +18090,7 @@
         <v>100506</v>
       </c>
       <c r="B511" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C511" t="s">
         <v>1286</v>
@@ -18105,7 +18105,7 @@
         <v>1288</v>
       </c>
       <c r="G511" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.25">
@@ -18128,7 +18128,7 @@
         <v>1288</v>
       </c>
       <c r="G512" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="513" spans="1:7" x14ac:dyDescent="0.25">
@@ -18151,7 +18151,7 @@
         <v>1288</v>
       </c>
       <c r="G513" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="514" spans="1:7" x14ac:dyDescent="0.25">
@@ -18174,7 +18174,7 @@
         <v>1288</v>
       </c>
       <c r="G514" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="515" spans="1:7" x14ac:dyDescent="0.25">
@@ -18197,7 +18197,7 @@
         <v>1288</v>
       </c>
       <c r="G515" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="516" spans="1:7" x14ac:dyDescent="0.25">
@@ -18220,7 +18220,7 @@
         <v>1288</v>
       </c>
       <c r="G516" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="517" spans="1:7" x14ac:dyDescent="0.25">
@@ -18266,7 +18266,7 @@
         <v>1303</v>
       </c>
       <c r="G518" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="519" spans="1:7" x14ac:dyDescent="0.25">
@@ -18289,7 +18289,7 @@
         <v>1307</v>
       </c>
       <c r="G519" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="520" spans="1:7" x14ac:dyDescent="0.25">
@@ -18312,7 +18312,7 @@
         <v>1307</v>
       </c>
       <c r="G520" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="521" spans="1:7" x14ac:dyDescent="0.25">
@@ -18335,7 +18335,7 @@
         <v>1313</v>
       </c>
       <c r="G521" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="522" spans="1:7" x14ac:dyDescent="0.25">
@@ -18358,7 +18358,7 @@
         <v>670</v>
       </c>
       <c r="G522" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="523" spans="1:7" x14ac:dyDescent="0.25">
@@ -18381,7 +18381,7 @@
         <v>1320</v>
       </c>
       <c r="G523" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="524" spans="1:7" x14ac:dyDescent="0.25">
@@ -18404,7 +18404,7 @@
         <v>370</v>
       </c>
       <c r="G524" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="525" spans="1:7" x14ac:dyDescent="0.25">
@@ -18427,7 +18427,7 @@
         <v>1327</v>
       </c>
       <c r="G525" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="526" spans="1:7" x14ac:dyDescent="0.25">
@@ -18450,7 +18450,7 @@
         <v>1331</v>
       </c>
       <c r="G526" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="527" spans="1:7" x14ac:dyDescent="0.25">
@@ -18473,7 +18473,7 @@
         <v>1331</v>
       </c>
       <c r="G527" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="528" spans="1:7" x14ac:dyDescent="0.25">
@@ -18496,7 +18496,7 @@
         <v>1331</v>
       </c>
       <c r="G528" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="529" spans="1:7" x14ac:dyDescent="0.25">
@@ -18519,7 +18519,7 @@
         <v>1338</v>
       </c>
       <c r="G529" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="530" spans="1:7" x14ac:dyDescent="0.25">
@@ -18542,7 +18542,7 @@
         <v>1338</v>
       </c>
       <c r="G530" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="531" spans="1:7" x14ac:dyDescent="0.25">
@@ -18565,7 +18565,7 @@
         <v>1338</v>
       </c>
       <c r="G531" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="532" spans="1:7" x14ac:dyDescent="0.25">
@@ -18588,7 +18588,7 @@
         <v>1338</v>
       </c>
       <c r="G532" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="533" spans="1:7" x14ac:dyDescent="0.25">
@@ -18611,7 +18611,7 @@
         <v>1338</v>
       </c>
       <c r="G533" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="534" spans="1:7" x14ac:dyDescent="0.25">
@@ -18634,7 +18634,7 @@
         <v>1338</v>
       </c>
       <c r="G534" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="535" spans="1:7" x14ac:dyDescent="0.25">
@@ -18657,7 +18657,7 @@
         <v>1090</v>
       </c>
       <c r="G535" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="536" spans="1:7" x14ac:dyDescent="0.25">
@@ -18680,7 +18680,7 @@
         <v>704</v>
       </c>
       <c r="G536" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="537" spans="1:7" x14ac:dyDescent="0.25">
@@ -18703,7 +18703,7 @@
         <v>1357</v>
       </c>
       <c r="G537" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="538" spans="1:7" x14ac:dyDescent="0.25">
@@ -18726,7 +18726,7 @@
         <v>1357</v>
       </c>
       <c r="G538" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="539" spans="1:7" x14ac:dyDescent="0.25">
@@ -18749,7 +18749,7 @@
         <v>1357</v>
       </c>
       <c r="G539" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="540" spans="1:7" x14ac:dyDescent="0.25">
@@ -18772,7 +18772,7 @@
         <v>1357</v>
       </c>
       <c r="G540" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="541" spans="1:7" x14ac:dyDescent="0.25">
@@ -18795,7 +18795,7 @@
         <v>1357</v>
       </c>
       <c r="G541" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="542" spans="1:7" x14ac:dyDescent="0.25">
@@ -18841,7 +18841,7 @@
         <v>1357</v>
       </c>
       <c r="G543" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="544" spans="1:7" x14ac:dyDescent="0.25">
@@ -18864,7 +18864,7 @@
         <v>1357</v>
       </c>
       <c r="G544" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="545" spans="1:7" x14ac:dyDescent="0.25">
@@ -18887,7 +18887,7 @@
         <v>1357</v>
       </c>
       <c r="G545" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="546" spans="1:7" x14ac:dyDescent="0.25">
@@ -18910,7 +18910,7 @@
         <v>1357</v>
       </c>
       <c r="G546" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.25">
@@ -18933,7 +18933,7 @@
         <v>1357</v>
       </c>
       <c r="G547" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="548" spans="1:7" x14ac:dyDescent="0.25">
@@ -18956,7 +18956,7 @@
         <v>1357</v>
       </c>
       <c r="G548" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="549" spans="1:7" x14ac:dyDescent="0.25">
@@ -18979,7 +18979,7 @@
         <v>1357</v>
       </c>
       <c r="G549" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="550" spans="1:7" x14ac:dyDescent="0.25">
@@ -19002,7 +19002,7 @@
         <v>1357</v>
       </c>
       <c r="G550" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="551" spans="1:7" x14ac:dyDescent="0.25">
@@ -19025,7 +19025,7 @@
         <v>1357</v>
       </c>
       <c r="G551" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="552" spans="1:7" x14ac:dyDescent="0.25">
@@ -19048,7 +19048,7 @@
         <v>1388</v>
       </c>
       <c r="G552" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="553" spans="1:7" x14ac:dyDescent="0.25">
@@ -19071,7 +19071,7 @@
         <v>1388</v>
       </c>
       <c r="G553" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="554" spans="1:7" x14ac:dyDescent="0.25">
@@ -19094,7 +19094,7 @@
         <v>1388</v>
       </c>
       <c r="G554" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="555" spans="1:7" x14ac:dyDescent="0.25">
@@ -19117,7 +19117,7 @@
         <v>1388</v>
       </c>
       <c r="G555" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="556" spans="1:7" x14ac:dyDescent="0.25">
@@ -19140,7 +19140,7 @@
         <v>1388</v>
       </c>
       <c r="G556" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="557" spans="1:7" x14ac:dyDescent="0.25">
@@ -19163,7 +19163,7 @@
         <v>1388</v>
       </c>
       <c r="G557" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.25">
@@ -19186,7 +19186,7 @@
         <v>1388</v>
       </c>
       <c r="G558" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="559" spans="1:7" x14ac:dyDescent="0.25">
@@ -19209,7 +19209,7 @@
         <v>1388</v>
       </c>
       <c r="G559" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="560" spans="1:7" x14ac:dyDescent="0.25">
@@ -19232,7 +19232,7 @@
         <v>1388</v>
       </c>
       <c r="G560" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.25">
@@ -19255,7 +19255,7 @@
         <v>1388</v>
       </c>
       <c r="G561" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="562" spans="1:7" x14ac:dyDescent="0.25">
@@ -19278,7 +19278,7 @@
         <v>1388</v>
       </c>
       <c r="G562" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="563" spans="1:7" x14ac:dyDescent="0.25">
@@ -19301,7 +19301,7 @@
         <v>1388</v>
       </c>
       <c r="G563" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="564" spans="1:7" x14ac:dyDescent="0.25">
@@ -19324,7 +19324,7 @@
         <v>1388</v>
       </c>
       <c r="G564" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="565" spans="1:7" x14ac:dyDescent="0.25">
@@ -19347,7 +19347,7 @@
         <v>1415</v>
       </c>
       <c r="G565" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="566" spans="1:7" x14ac:dyDescent="0.25">
@@ -19370,7 +19370,7 @@
         <v>1415</v>
       </c>
       <c r="G566" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="567" spans="1:7" x14ac:dyDescent="0.25">
@@ -19416,7 +19416,7 @@
         <v>1415</v>
       </c>
       <c r="G568" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="569" spans="1:7" x14ac:dyDescent="0.25">
@@ -19439,7 +19439,7 @@
         <v>1415</v>
       </c>
       <c r="G569" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="570" spans="1:7" x14ac:dyDescent="0.25">
@@ -19462,7 +19462,7 @@
         <v>1415</v>
       </c>
       <c r="G570" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.25">
@@ -19485,7 +19485,7 @@
         <v>1415</v>
       </c>
       <c r="G571" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.25">
@@ -19508,7 +19508,7 @@
         <v>1415</v>
       </c>
       <c r="G572" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="573" spans="1:7" x14ac:dyDescent="0.25">
@@ -19531,7 +19531,7 @@
         <v>1415</v>
       </c>
       <c r="G573" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="574" spans="1:7" x14ac:dyDescent="0.25">
@@ -19554,7 +19554,7 @@
         <v>1415</v>
       </c>
       <c r="G574" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="575" spans="1:7" x14ac:dyDescent="0.25">
@@ -19577,7 +19577,7 @@
         <v>1415</v>
       </c>
       <c r="G575" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="576" spans="1:7" x14ac:dyDescent="0.25">
@@ -19600,7 +19600,7 @@
         <v>1415</v>
       </c>
       <c r="G576" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="577" spans="1:7" x14ac:dyDescent="0.25">
@@ -19623,7 +19623,7 @@
         <v>1415</v>
       </c>
       <c r="G577" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="578" spans="1:7" x14ac:dyDescent="0.25">
@@ -19646,7 +19646,7 @@
         <v>1415</v>
       </c>
       <c r="G578" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="579" spans="1:7" x14ac:dyDescent="0.25">
@@ -19669,7 +19669,7 @@
         <v>1440</v>
       </c>
       <c r="G579" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="580" spans="1:7" x14ac:dyDescent="0.25">
@@ -19692,7 +19692,7 @@
         <v>1444</v>
       </c>
       <c r="G580" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="581" spans="1:7" x14ac:dyDescent="0.25">
@@ -19715,7 +19715,7 @@
         <v>1448</v>
       </c>
       <c r="G581" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="582" spans="1:7" x14ac:dyDescent="0.25">
@@ -19738,7 +19738,7 @@
         <v>1448</v>
       </c>
       <c r="G582" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="583" spans="1:7" x14ac:dyDescent="0.25">
@@ -19761,7 +19761,7 @@
         <v>1453</v>
       </c>
       <c r="G583" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="584" spans="1:7" x14ac:dyDescent="0.25">
@@ -19784,7 +19784,7 @@
         <v>1453</v>
       </c>
       <c r="G584" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="585" spans="1:7" x14ac:dyDescent="0.25">
@@ -19807,7 +19807,7 @@
         <v>1453</v>
       </c>
       <c r="G585" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="586" spans="1:7" x14ac:dyDescent="0.25">
@@ -19830,7 +19830,7 @@
         <v>1453</v>
       </c>
       <c r="G586" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="587" spans="1:7" x14ac:dyDescent="0.25">
@@ -19853,7 +19853,7 @@
         <v>1453</v>
       </c>
       <c r="G587" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="588" spans="1:7" x14ac:dyDescent="0.25">
@@ -19876,7 +19876,7 @@
         <v>1453</v>
       </c>
       <c r="G588" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.25">
@@ -19899,7 +19899,7 @@
         <v>1453</v>
       </c>
       <c r="G589" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="590" spans="1:7" x14ac:dyDescent="0.25">
@@ -19922,7 +19922,7 @@
         <v>1453</v>
       </c>
       <c r="G590" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="591" spans="1:7" x14ac:dyDescent="0.25">
@@ -19945,7 +19945,7 @@
         <v>1453</v>
       </c>
       <c r="G591" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="592" spans="1:7" x14ac:dyDescent="0.25">
@@ -19968,7 +19968,7 @@
         <v>1453</v>
       </c>
       <c r="G592" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="593" spans="1:7" x14ac:dyDescent="0.25">
@@ -19991,7 +19991,7 @@
         <v>1453</v>
       </c>
       <c r="G593" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="594" spans="1:7" x14ac:dyDescent="0.25">
@@ -20014,7 +20014,7 @@
         <v>1453</v>
       </c>
       <c r="G594" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="595" spans="1:7" x14ac:dyDescent="0.25">
@@ -20037,7 +20037,7 @@
         <v>1320</v>
       </c>
       <c r="G595" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="596" spans="1:7" x14ac:dyDescent="0.25">
@@ -20060,7 +20060,7 @@
         <v>500</v>
       </c>
       <c r="G596" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="597" spans="1:7" x14ac:dyDescent="0.25">
@@ -20106,7 +20106,7 @@
         <v>500</v>
       </c>
       <c r="G598" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="599" spans="1:7" x14ac:dyDescent="0.25">
@@ -20129,7 +20129,7 @@
         <v>500</v>
       </c>
       <c r="G599" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="600" spans="1:7" x14ac:dyDescent="0.25">
@@ -20198,7 +20198,7 @@
         <v>500</v>
       </c>
       <c r="G602" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="603" spans="1:7" x14ac:dyDescent="0.25">
@@ -20221,7 +20221,7 @@
         <v>500</v>
       </c>
       <c r="G603" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="604" spans="1:7" x14ac:dyDescent="0.25">
@@ -20244,7 +20244,7 @@
         <v>500</v>
       </c>
       <c r="G604" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="605" spans="1:7" x14ac:dyDescent="0.25">
@@ -20267,7 +20267,7 @@
         <v>500</v>
       </c>
       <c r="G605" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="606" spans="1:7" x14ac:dyDescent="0.25">
@@ -20290,7 +20290,7 @@
         <v>500</v>
       </c>
       <c r="G606" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="607" spans="1:7" x14ac:dyDescent="0.25">
@@ -20313,7 +20313,7 @@
         <v>500</v>
       </c>
       <c r="G607" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="608" spans="1:7" x14ac:dyDescent="0.25">
@@ -20336,7 +20336,7 @@
         <v>500</v>
       </c>
       <c r="G608" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="609" spans="1:7" x14ac:dyDescent="0.25">
@@ -20359,7 +20359,7 @@
         <v>500</v>
       </c>
       <c r="G609" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="610" spans="1:7" x14ac:dyDescent="0.25">
@@ -20382,7 +20382,7 @@
         <v>500</v>
       </c>
       <c r="G610" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="611" spans="1:7" x14ac:dyDescent="0.25">
@@ -20405,7 +20405,7 @@
         <v>1506</v>
       </c>
       <c r="G611" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="612" spans="1:7" x14ac:dyDescent="0.25">
@@ -20428,7 +20428,7 @@
         <v>1506</v>
       </c>
       <c r="G612" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="613" spans="1:7" x14ac:dyDescent="0.25">
@@ -20451,7 +20451,7 @@
         <v>1506</v>
       </c>
       <c r="G613" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="614" spans="1:7" x14ac:dyDescent="0.25">
@@ -20474,7 +20474,7 @@
         <v>1506</v>
       </c>
       <c r="G614" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="615" spans="1:7" x14ac:dyDescent="0.25">
@@ -20497,7 +20497,7 @@
         <v>1506</v>
       </c>
       <c r="G615" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="616" spans="1:7" x14ac:dyDescent="0.25">
@@ -20520,7 +20520,7 @@
         <v>1506</v>
       </c>
       <c r="G616" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="617" spans="1:7" x14ac:dyDescent="0.25">
@@ -20543,7 +20543,7 @@
         <v>1506</v>
       </c>
       <c r="G617" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="618" spans="1:7" x14ac:dyDescent="0.25">
@@ -20566,7 +20566,7 @@
         <v>1506</v>
       </c>
       <c r="G618" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="619" spans="1:7" x14ac:dyDescent="0.25">
@@ -20589,7 +20589,7 @@
         <v>1506</v>
       </c>
       <c r="G619" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="620" spans="1:7" x14ac:dyDescent="0.25">
@@ -20612,7 +20612,7 @@
         <v>1506</v>
       </c>
       <c r="G620" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="621" spans="1:7" x14ac:dyDescent="0.25">
@@ -20635,7 +20635,7 @@
         <v>1506</v>
       </c>
       <c r="G621" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="622" spans="1:7" x14ac:dyDescent="0.25">
@@ -20658,7 +20658,7 @@
         <v>1506</v>
       </c>
       <c r="G622" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="623" spans="1:7" x14ac:dyDescent="0.25">
@@ -20681,7 +20681,7 @@
         <v>1529</v>
       </c>
       <c r="G623" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="624" spans="1:7" x14ac:dyDescent="0.25">
@@ -20704,7 +20704,7 @@
         <v>1475</v>
       </c>
       <c r="G624" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="625" spans="1:7" x14ac:dyDescent="0.25">
@@ -20727,7 +20727,7 @@
         <v>952</v>
       </c>
       <c r="G625" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="626" spans="1:7" x14ac:dyDescent="0.25">
@@ -20750,7 +20750,7 @@
         <v>98</v>
       </c>
       <c r="G626" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="627" spans="1:7" x14ac:dyDescent="0.25">
@@ -20773,7 +20773,7 @@
         <v>197</v>
       </c>
       <c r="G627" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="628" spans="1:7" x14ac:dyDescent="0.25">
@@ -20796,7 +20796,7 @@
         <v>197</v>
       </c>
       <c r="G628" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="629" spans="1:7" x14ac:dyDescent="0.25">
@@ -20819,7 +20819,7 @@
         <v>197</v>
       </c>
       <c r="G629" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="630" spans="1:7" x14ac:dyDescent="0.25">
@@ -20842,7 +20842,7 @@
         <v>197</v>
       </c>
       <c r="G630" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="631" spans="1:7" x14ac:dyDescent="0.25">
@@ -20865,7 +20865,7 @@
         <v>197</v>
       </c>
       <c r="G631" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="632" spans="1:7" x14ac:dyDescent="0.25">
@@ -20888,7 +20888,7 @@
         <v>1550</v>
       </c>
       <c r="G632" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="633" spans="1:7" x14ac:dyDescent="0.25">
@@ -20911,7 +20911,7 @@
         <v>1550</v>
       </c>
       <c r="G633" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="634" spans="1:7" x14ac:dyDescent="0.25">
@@ -20934,7 +20934,7 @@
         <v>1550</v>
       </c>
       <c r="G634" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="635" spans="1:7" x14ac:dyDescent="0.25">
@@ -20957,7 +20957,7 @@
         <v>1550</v>
       </c>
       <c r="G635" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="636" spans="1:7" x14ac:dyDescent="0.25">
@@ -20980,7 +20980,7 @@
         <v>1550</v>
       </c>
       <c r="G636" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="637" spans="1:7" x14ac:dyDescent="0.25">
@@ -21003,7 +21003,7 @@
         <v>1550</v>
       </c>
       <c r="G637" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="638" spans="1:7" x14ac:dyDescent="0.25">
@@ -21026,7 +21026,7 @@
         <v>1550</v>
       </c>
       <c r="G638" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="639" spans="1:7" x14ac:dyDescent="0.25">
@@ -21049,7 +21049,7 @@
         <v>1550</v>
       </c>
       <c r="G639" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="640" spans="1:7" x14ac:dyDescent="0.25">
@@ -21072,7 +21072,7 @@
         <v>1568</v>
       </c>
       <c r="G640" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="641" spans="1:7" x14ac:dyDescent="0.25">
@@ -21118,7 +21118,7 @@
         <v>1568</v>
       </c>
       <c r="G642" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="643" spans="1:7" x14ac:dyDescent="0.25">
@@ -21141,7 +21141,7 @@
         <v>1568</v>
       </c>
       <c r="G643" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="644" spans="1:7" x14ac:dyDescent="0.25">
@@ -21164,7 +21164,7 @@
         <v>1568</v>
       </c>
       <c r="G644" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="645" spans="1:7" x14ac:dyDescent="0.25">
@@ -21187,7 +21187,7 @@
         <v>1568</v>
       </c>
       <c r="G645" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="646" spans="1:7" x14ac:dyDescent="0.25">
@@ -21210,7 +21210,7 @@
         <v>1568</v>
       </c>
       <c r="G646" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="647" spans="1:7" x14ac:dyDescent="0.25">
@@ -21233,7 +21233,7 @@
         <v>1568</v>
       </c>
       <c r="G647" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="648" spans="1:7" x14ac:dyDescent="0.25">
@@ -21256,7 +21256,7 @@
         <v>1568</v>
       </c>
       <c r="G648" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="649" spans="1:7" x14ac:dyDescent="0.25">
@@ -21302,7 +21302,7 @@
         <v>1489</v>
       </c>
       <c r="G650" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="651" spans="1:7" x14ac:dyDescent="0.25">
@@ -21325,7 +21325,7 @@
         <v>1489</v>
       </c>
       <c r="G651" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="652" spans="1:7" x14ac:dyDescent="0.25">
@@ -21348,7 +21348,7 @@
         <v>1489</v>
       </c>
       <c r="G652" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="653" spans="1:7" x14ac:dyDescent="0.25">
@@ -21371,7 +21371,7 @@
         <v>1489</v>
       </c>
       <c r="G653" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="654" spans="1:7" x14ac:dyDescent="0.25">
@@ -21394,7 +21394,7 @@
         <v>1489</v>
       </c>
       <c r="G654" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="655" spans="1:7" x14ac:dyDescent="0.25">
@@ -21417,7 +21417,7 @@
         <v>1489</v>
       </c>
       <c r="G655" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="656" spans="1:7" x14ac:dyDescent="0.25">
@@ -21440,7 +21440,7 @@
         <v>1489</v>
       </c>
       <c r="G656" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="657" spans="1:7" x14ac:dyDescent="0.25">
@@ -21463,7 +21463,7 @@
         <v>1489</v>
       </c>
       <c r="G657" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="658" spans="1:7" x14ac:dyDescent="0.25">
@@ -21486,7 +21486,7 @@
         <v>1489</v>
       </c>
       <c r="G658" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="659" spans="1:7" x14ac:dyDescent="0.25">
@@ -21509,7 +21509,7 @@
         <v>1604</v>
       </c>
       <c r="G659" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="660" spans="1:7" x14ac:dyDescent="0.25">
@@ -21532,7 +21532,7 @@
         <v>1604</v>
       </c>
       <c r="G660" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="661" spans="1:7" x14ac:dyDescent="0.25">
@@ -21555,7 +21555,7 @@
         <v>1604</v>
       </c>
       <c r="G661" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="662" spans="1:7" x14ac:dyDescent="0.25">
@@ -21578,7 +21578,7 @@
         <v>1604</v>
       </c>
       <c r="G662" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="663" spans="1:7" x14ac:dyDescent="0.25">
@@ -21601,7 +21601,7 @@
         <v>1604</v>
       </c>
       <c r="G663" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="664" spans="1:7" x14ac:dyDescent="0.25">
@@ -21647,7 +21647,7 @@
         <v>1604</v>
       </c>
       <c r="G665" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="666" spans="1:7" x14ac:dyDescent="0.25">
@@ -21670,7 +21670,7 @@
         <v>1619</v>
       </c>
       <c r="G666" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="667" spans="1:7" x14ac:dyDescent="0.25">
@@ -21693,7 +21693,7 @@
         <v>1100</v>
       </c>
       <c r="G667" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="668" spans="1:7" x14ac:dyDescent="0.25">
@@ -21716,7 +21716,7 @@
         <v>1509</v>
       </c>
       <c r="G668" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="669" spans="1:7" x14ac:dyDescent="0.25">
@@ -21739,7 +21739,7 @@
         <v>1628</v>
       </c>
       <c r="G669" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="670" spans="1:7" x14ac:dyDescent="0.25">
@@ -21785,7 +21785,7 @@
         <v>1634</v>
       </c>
       <c r="G671" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="672" spans="1:7" x14ac:dyDescent="0.25">
@@ -21808,7 +21808,7 @@
         <v>1634</v>
       </c>
       <c r="G672" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="673" spans="1:7" x14ac:dyDescent="0.25">
@@ -21831,7 +21831,7 @@
         <v>1634</v>
       </c>
       <c r="G673" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="674" spans="1:7" x14ac:dyDescent="0.25">
@@ -21854,7 +21854,7 @@
         <v>1634</v>
       </c>
       <c r="G674" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="675" spans="1:7" x14ac:dyDescent="0.25">
@@ -21877,7 +21877,7 @@
         <v>1644</v>
       </c>
       <c r="G675" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="676" spans="1:7" x14ac:dyDescent="0.25">
@@ -21900,7 +21900,7 @@
         <v>1644</v>
       </c>
       <c r="G676" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="677" spans="1:7" x14ac:dyDescent="0.25">
@@ -21923,7 +21923,7 @@
         <v>1644</v>
       </c>
       <c r="G677" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="678" spans="1:7" x14ac:dyDescent="0.25">
@@ -21946,7 +21946,7 @@
         <v>1644</v>
       </c>
       <c r="G678" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="679" spans="1:7" x14ac:dyDescent="0.25">
@@ -21969,7 +21969,7 @@
         <v>1653</v>
       </c>
       <c r="G679" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="680" spans="1:7" x14ac:dyDescent="0.25">
@@ -21992,7 +21992,7 @@
         <v>1653</v>
       </c>
       <c r="G680" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="681" spans="1:7" x14ac:dyDescent="0.25">
@@ -22015,7 +22015,7 @@
         <v>1653</v>
       </c>
       <c r="G681" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="682" spans="1:7" x14ac:dyDescent="0.25">
@@ -22038,7 +22038,7 @@
         <v>1653</v>
       </c>
       <c r="G682" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="683" spans="1:7" x14ac:dyDescent="0.25">
@@ -22061,7 +22061,7 @@
         <v>1653</v>
       </c>
       <c r="G683" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="684" spans="1:7" x14ac:dyDescent="0.25">
@@ -22084,7 +22084,7 @@
         <v>1653</v>
       </c>
       <c r="G684" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="685" spans="1:7" x14ac:dyDescent="0.25">
@@ -22107,7 +22107,7 @@
         <v>1653</v>
       </c>
       <c r="G685" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="686" spans="1:7" x14ac:dyDescent="0.25">
@@ -22130,7 +22130,7 @@
         <v>1653</v>
       </c>
       <c r="G686" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="687" spans="1:7" x14ac:dyDescent="0.25">
@@ -22153,7 +22153,7 @@
         <v>1669</v>
       </c>
       <c r="G687" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="688" spans="1:7" x14ac:dyDescent="0.25">
@@ -22176,7 +22176,7 @@
         <v>1669</v>
       </c>
       <c r="G688" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="689" spans="1:7" x14ac:dyDescent="0.25">
@@ -22199,7 +22199,7 @@
         <v>1669</v>
       </c>
       <c r="G689" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="690" spans="1:7" x14ac:dyDescent="0.25">
@@ -22222,7 +22222,7 @@
         <v>1669</v>
       </c>
       <c r="G690" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="691" spans="1:7" x14ac:dyDescent="0.25">
@@ -22245,7 +22245,7 @@
         <v>1669</v>
       </c>
       <c r="G691" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="692" spans="1:7" x14ac:dyDescent="0.25">
@@ -22268,7 +22268,7 @@
         <v>1669</v>
       </c>
       <c r="G692" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="693" spans="1:7" x14ac:dyDescent="0.25">
@@ -22291,7 +22291,7 @@
         <v>1681</v>
       </c>
       <c r="G693" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="694" spans="1:7" x14ac:dyDescent="0.25">
@@ -22314,7 +22314,7 @@
         <v>197</v>
       </c>
       <c r="G694" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="695" spans="1:7" x14ac:dyDescent="0.25">
@@ -22337,7 +22337,7 @@
         <v>954</v>
       </c>
       <c r="G695" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="696" spans="1:7" x14ac:dyDescent="0.25">
@@ -22360,7 +22360,7 @@
         <v>954</v>
       </c>
       <c r="G696" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="697" spans="1:7" x14ac:dyDescent="0.25">
@@ -22383,7 +22383,7 @@
         <v>1141</v>
       </c>
       <c r="G697" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="698" spans="1:7" x14ac:dyDescent="0.25">
@@ -22406,7 +22406,7 @@
         <v>1141</v>
       </c>
       <c r="G698" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="699" spans="1:7" x14ac:dyDescent="0.25">
@@ -22429,7 +22429,7 @@
         <v>1141</v>
       </c>
       <c r="G699" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="700" spans="1:7" x14ac:dyDescent="0.25">
@@ -22452,7 +22452,7 @@
         <v>1141</v>
       </c>
       <c r="G700" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="701" spans="1:7" x14ac:dyDescent="0.25">
@@ -22475,7 +22475,7 @@
         <v>1141</v>
       </c>
       <c r="G701" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="702" spans="1:7" x14ac:dyDescent="0.25">
@@ -22498,7 +22498,7 @@
         <v>1141</v>
       </c>
       <c r="G702" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="703" spans="1:7" x14ac:dyDescent="0.25">
@@ -22521,7 +22521,7 @@
         <v>1141</v>
       </c>
       <c r="G703" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="704" spans="1:7" x14ac:dyDescent="0.25">
@@ -22544,7 +22544,7 @@
         <v>1141</v>
       </c>
       <c r="G704" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="705" spans="1:7" x14ac:dyDescent="0.25">
@@ -22567,7 +22567,7 @@
         <v>1141</v>
       </c>
       <c r="G705" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="706" spans="1:7" x14ac:dyDescent="0.25">
@@ -22590,7 +22590,7 @@
         <v>1141</v>
       </c>
       <c r="G706" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="707" spans="1:7" x14ac:dyDescent="0.25">
@@ -22613,7 +22613,7 @@
         <v>1141</v>
       </c>
       <c r="G707" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="708" spans="1:7" x14ac:dyDescent="0.25">
@@ -22636,7 +22636,7 @@
         <v>1141</v>
       </c>
       <c r="G708" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="709" spans="1:7" x14ac:dyDescent="0.25">
@@ -22659,7 +22659,7 @@
         <v>1141</v>
       </c>
       <c r="G709" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="710" spans="1:7" x14ac:dyDescent="0.25">
@@ -22682,7 +22682,7 @@
         <v>1141</v>
       </c>
       <c r="G710" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="711" spans="1:7" x14ac:dyDescent="0.25">
@@ -22705,7 +22705,7 @@
         <v>1141</v>
       </c>
       <c r="G711" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="712" spans="1:7" x14ac:dyDescent="0.25">
@@ -22728,7 +22728,7 @@
         <v>1141</v>
       </c>
       <c r="G712" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="713" spans="1:7" x14ac:dyDescent="0.25">
@@ -22751,7 +22751,7 @@
         <v>1141</v>
       </c>
       <c r="G713" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="714" spans="1:7" x14ac:dyDescent="0.25">
@@ -22797,7 +22797,7 @@
         <v>1729</v>
       </c>
       <c r="G715" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="716" spans="1:7" x14ac:dyDescent="0.25">
@@ -22820,7 +22820,7 @@
         <v>1729</v>
       </c>
       <c r="G716" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="717" spans="1:7" x14ac:dyDescent="0.25">
@@ -22866,7 +22866,7 @@
         <v>1738</v>
       </c>
       <c r="G718" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="719" spans="1:7" x14ac:dyDescent="0.25">
@@ -22889,7 +22889,7 @@
         <v>1349</v>
       </c>
       <c r="G719" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="720" spans="1:7" x14ac:dyDescent="0.25">
@@ -22912,7 +22912,7 @@
         <v>1742</v>
       </c>
       <c r="G720" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="721" spans="1:7" x14ac:dyDescent="0.25">
@@ -22935,7 +22935,7 @@
         <v>1746</v>
       </c>
       <c r="G721" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="722" spans="1:7" x14ac:dyDescent="0.25">
@@ -22958,7 +22958,7 @@
         <v>1749</v>
       </c>
       <c r="G722" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="723" spans="1:7" x14ac:dyDescent="0.25">
@@ -22981,7 +22981,7 @@
         <v>1644</v>
       </c>
       <c r="G723" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="724" spans="1:7" x14ac:dyDescent="0.25">
@@ -23004,7 +23004,7 @@
         <v>1644</v>
       </c>
       <c r="G724" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="725" spans="1:7" x14ac:dyDescent="0.25">
@@ -23027,7 +23027,7 @@
         <v>1644</v>
       </c>
       <c r="G725" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="726" spans="1:7" x14ac:dyDescent="0.25">
@@ -23050,7 +23050,7 @@
         <v>1644</v>
       </c>
       <c r="G726" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="727" spans="1:7" x14ac:dyDescent="0.25">
@@ -23073,7 +23073,7 @@
         <v>1644</v>
       </c>
       <c r="G727" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="728" spans="1:7" x14ac:dyDescent="0.25">
@@ -23096,7 +23096,7 @@
         <v>1644</v>
       </c>
       <c r="G728" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="729" spans="1:7" x14ac:dyDescent="0.25">
@@ -23119,7 +23119,7 @@
         <v>1644</v>
       </c>
       <c r="G729" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="730" spans="1:7" x14ac:dyDescent="0.25">
@@ -23165,7 +23165,7 @@
         <v>1770</v>
       </c>
       <c r="G731" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="732" spans="1:7" x14ac:dyDescent="0.25">
@@ -23188,7 +23188,7 @@
         <v>1770</v>
       </c>
       <c r="G732" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="733" spans="1:7" x14ac:dyDescent="0.25">
@@ -23211,7 +23211,7 @@
         <v>1770</v>
       </c>
       <c r="G733" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="734" spans="1:7" x14ac:dyDescent="0.25">
@@ -23234,7 +23234,7 @@
         <v>1777</v>
       </c>
       <c r="G734" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="735" spans="1:7" x14ac:dyDescent="0.25">
@@ -23257,7 +23257,7 @@
         <v>1634</v>
       </c>
       <c r="G735" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="736" spans="1:7" x14ac:dyDescent="0.25">
@@ -23280,7 +23280,7 @@
         <v>1634</v>
       </c>
       <c r="G736" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="737" spans="1:7" x14ac:dyDescent="0.25">
@@ -23303,7 +23303,7 @@
         <v>1787</v>
       </c>
       <c r="G737" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="738" spans="1:7" x14ac:dyDescent="0.25">
@@ -23326,7 +23326,7 @@
         <v>1792</v>
       </c>
       <c r="G738" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="739" spans="1:7" x14ac:dyDescent="0.25">
@@ -23349,7 +23349,7 @@
         <v>1792</v>
       </c>
       <c r="G739" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="740" spans="1:7" x14ac:dyDescent="0.25">
@@ -23372,7 +23372,7 @@
         <v>1792</v>
       </c>
       <c r="G740" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="741" spans="1:7" x14ac:dyDescent="0.25">
@@ -23395,7 +23395,7 @@
         <v>1799</v>
       </c>
       <c r="G741" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="742" spans="1:7" x14ac:dyDescent="0.25">
@@ -23418,7 +23418,7 @@
         <v>1803</v>
       </c>
       <c r="G742" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="743" spans="1:7" x14ac:dyDescent="0.25">
@@ -23441,7 +23441,7 @@
         <v>1784</v>
       </c>
       <c r="G743" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="744" spans="1:7" x14ac:dyDescent="0.25">
@@ -23464,7 +23464,7 @@
         <v>711</v>
       </c>
       <c r="G744" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="745" spans="1:7" x14ac:dyDescent="0.25">
@@ -23487,7 +23487,7 @@
         <v>711</v>
       </c>
       <c r="G745" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="746" spans="1:7" x14ac:dyDescent="0.25">
@@ -23510,7 +23510,7 @@
         <v>711</v>
       </c>
       <c r="G746" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="747" spans="1:7" x14ac:dyDescent="0.25">
@@ -23533,7 +23533,7 @@
         <v>711</v>
       </c>
       <c r="G747" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="748" spans="1:7" x14ac:dyDescent="0.25">
@@ -23556,7 +23556,7 @@
         <v>711</v>
       </c>
       <c r="G748" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="749" spans="1:7" x14ac:dyDescent="0.25">
@@ -23579,7 +23579,7 @@
         <v>711</v>
       </c>
       <c r="G749" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="750" spans="1:7" x14ac:dyDescent="0.25">
@@ -23602,7 +23602,7 @@
         <v>711</v>
       </c>
       <c r="G750" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="751" spans="1:7" x14ac:dyDescent="0.25">
@@ -23625,7 +23625,7 @@
         <v>711</v>
       </c>
       <c r="G751" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="752" spans="1:7" x14ac:dyDescent="0.25">
@@ -23648,7 +23648,7 @@
         <v>711</v>
       </c>
       <c r="G752" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="753" spans="1:7" x14ac:dyDescent="0.25">
@@ -23671,7 +23671,7 @@
         <v>711</v>
       </c>
       <c r="G753" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="754" spans="1:7" x14ac:dyDescent="0.25">
@@ -23694,7 +23694,7 @@
         <v>711</v>
       </c>
       <c r="G754" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="755" spans="1:7" x14ac:dyDescent="0.25">
@@ -23717,7 +23717,7 @@
         <v>711</v>
       </c>
       <c r="G755" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="756" spans="1:7" x14ac:dyDescent="0.25">
@@ -23740,7 +23740,7 @@
         <v>711</v>
       </c>
       <c r="G756" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="757" spans="1:7" x14ac:dyDescent="0.25">
@@ -23763,7 +23763,7 @@
         <v>711</v>
       </c>
       <c r="G757" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="758" spans="1:7" x14ac:dyDescent="0.25">
@@ -23786,7 +23786,7 @@
         <v>711</v>
       </c>
       <c r="G758" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="759" spans="1:7" x14ac:dyDescent="0.25">
@@ -23809,7 +23809,7 @@
         <v>711</v>
       </c>
       <c r="G759" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="760" spans="1:7" x14ac:dyDescent="0.25">
@@ -23832,7 +23832,7 @@
         <v>711</v>
       </c>
       <c r="G760" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="761" spans="1:7" x14ac:dyDescent="0.25">
@@ -23855,7 +23855,7 @@
         <v>711</v>
       </c>
       <c r="G761" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="762" spans="1:7" x14ac:dyDescent="0.25">
@@ -23878,7 +23878,7 @@
         <v>711</v>
       </c>
       <c r="G762" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="763" spans="1:7" x14ac:dyDescent="0.25">
@@ -23901,7 +23901,7 @@
         <v>711</v>
       </c>
       <c r="G763" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="764" spans="1:7" x14ac:dyDescent="0.25">
@@ -23924,7 +23924,7 @@
         <v>711</v>
       </c>
       <c r="G764" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="765" spans="1:7" x14ac:dyDescent="0.25">
@@ -23947,7 +23947,7 @@
         <v>711</v>
       </c>
       <c r="G765" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="766" spans="1:7" x14ac:dyDescent="0.25">
@@ -23970,7 +23970,7 @@
         <v>711</v>
       </c>
       <c r="G766" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="767" spans="1:7" x14ac:dyDescent="0.25">
@@ -24016,7 +24016,7 @@
         <v>711</v>
       </c>
       <c r="G768" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="769" spans="1:7" x14ac:dyDescent="0.25">
@@ -24039,7 +24039,7 @@
         <v>711</v>
       </c>
       <c r="G769" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="770" spans="1:7" x14ac:dyDescent="0.25">
@@ -24062,7 +24062,7 @@
         <v>711</v>
       </c>
       <c r="G770" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="771" spans="1:7" x14ac:dyDescent="0.25">
@@ -24085,7 +24085,7 @@
         <v>711</v>
       </c>
       <c r="G771" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="772" spans="1:7" x14ac:dyDescent="0.25">
@@ -24108,7 +24108,7 @@
         <v>711</v>
       </c>
       <c r="G772" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="773" spans="1:7" x14ac:dyDescent="0.25">
@@ -24131,7 +24131,7 @@
         <v>711</v>
       </c>
       <c r="G773" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="774" spans="1:7" x14ac:dyDescent="0.25">
@@ -24154,7 +24154,7 @@
         <v>711</v>
       </c>
       <c r="G774" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="775" spans="1:7" x14ac:dyDescent="0.25">
@@ -24177,7 +24177,7 @@
         <v>711</v>
       </c>
       <c r="G775" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="776" spans="1:7" x14ac:dyDescent="0.25">
@@ -24200,7 +24200,7 @@
         <v>711</v>
       </c>
       <c r="G776" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="777" spans="1:7" x14ac:dyDescent="0.25">
@@ -24223,7 +24223,7 @@
         <v>711</v>
       </c>
       <c r="G777" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="778" spans="1:7" x14ac:dyDescent="0.25">
@@ -24246,7 +24246,7 @@
         <v>711</v>
       </c>
       <c r="G778" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="779" spans="1:7" x14ac:dyDescent="0.25">
@@ -24269,7 +24269,7 @@
         <v>711</v>
       </c>
       <c r="G779" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="780" spans="1:7" x14ac:dyDescent="0.25">
@@ -24292,7 +24292,7 @@
         <v>711</v>
       </c>
       <c r="G780" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="781" spans="1:7" x14ac:dyDescent="0.25">
@@ -24315,7 +24315,7 @@
         <v>711</v>
       </c>
       <c r="G781" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="782" spans="1:7" x14ac:dyDescent="0.25">
@@ -24338,7 +24338,7 @@
         <v>711</v>
       </c>
       <c r="G782" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="783" spans="1:7" x14ac:dyDescent="0.25">
@@ -24361,7 +24361,7 @@
         <v>711</v>
       </c>
       <c r="G783" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="784" spans="1:7" x14ac:dyDescent="0.25">
@@ -24384,7 +24384,7 @@
         <v>711</v>
       </c>
       <c r="G784" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="785" spans="1:7" x14ac:dyDescent="0.25">
@@ -24407,7 +24407,7 @@
         <v>711</v>
       </c>
       <c r="G785" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="786" spans="1:7" x14ac:dyDescent="0.25">
@@ -24430,7 +24430,7 @@
         <v>711</v>
       </c>
       <c r="G786" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="787" spans="1:7" x14ac:dyDescent="0.25">
@@ -24453,7 +24453,7 @@
         <v>711</v>
       </c>
       <c r="G787" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="788" spans="1:7" x14ac:dyDescent="0.25">
@@ -24476,7 +24476,7 @@
         <v>711</v>
       </c>
       <c r="G788" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="789" spans="1:7" x14ac:dyDescent="0.25">
@@ -24499,7 +24499,7 @@
         <v>1892</v>
       </c>
       <c r="G789" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="790" spans="1:7" x14ac:dyDescent="0.25">
@@ -24522,7 +24522,7 @@
         <v>1892</v>
       </c>
       <c r="G790" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="791" spans="1:7" x14ac:dyDescent="0.25">
@@ -24545,7 +24545,7 @@
         <v>1892</v>
       </c>
       <c r="G791" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="792" spans="1:7" x14ac:dyDescent="0.25">
@@ -24568,7 +24568,7 @@
         <v>1892</v>
       </c>
       <c r="G792" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="793" spans="1:7" x14ac:dyDescent="0.25">
@@ -24576,7 +24576,7 @@
         <v>100788</v>
       </c>
       <c r="B793" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C793" t="s">
         <v>1899</v>
@@ -24591,7 +24591,7 @@
         <v>1892</v>
       </c>
       <c r="G793" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="794" spans="1:7" x14ac:dyDescent="0.25">
@@ -24614,7 +24614,7 @@
         <v>1892</v>
       </c>
       <c r="G794" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="795" spans="1:7" x14ac:dyDescent="0.25">
@@ -24637,7 +24637,7 @@
         <v>1892</v>
       </c>
       <c r="G795" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="796" spans="1:7" x14ac:dyDescent="0.25">
@@ -24660,7 +24660,7 @@
         <v>1892</v>
       </c>
       <c r="G796" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="797" spans="1:7" x14ac:dyDescent="0.25">
@@ -24683,7 +24683,7 @@
         <v>1892</v>
       </c>
       <c r="G797" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="798" spans="1:7" x14ac:dyDescent="0.25">
@@ -24706,7 +24706,7 @@
         <v>1911</v>
       </c>
       <c r="G798" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="799" spans="1:7" x14ac:dyDescent="0.25">
@@ -24729,7 +24729,7 @@
         <v>1911</v>
       </c>
       <c r="G799" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="800" spans="1:7" x14ac:dyDescent="0.25">
@@ -24752,7 +24752,7 @@
         <v>1911</v>
       </c>
       <c r="G800" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="801" spans="1:7" x14ac:dyDescent="0.25">
@@ -24775,7 +24775,7 @@
         <v>1911</v>
       </c>
       <c r="G801" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="802" spans="1:7" x14ac:dyDescent="0.25">
@@ -24798,7 +24798,7 @@
         <v>1911</v>
       </c>
       <c r="G802" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="803" spans="1:7" x14ac:dyDescent="0.25">
@@ -24821,7 +24821,7 @@
         <v>1921</v>
       </c>
       <c r="G803" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="804" spans="1:7" x14ac:dyDescent="0.25">
@@ -24844,7 +24844,7 @@
         <v>375</v>
       </c>
       <c r="G804" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="805" spans="1:7" x14ac:dyDescent="0.25">
@@ -24867,7 +24867,7 @@
         <v>375</v>
       </c>
       <c r="G805" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="806" spans="1:7" x14ac:dyDescent="0.25">
@@ -24890,7 +24890,7 @@
         <v>1930</v>
       </c>
       <c r="G806" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="807" spans="1:7" x14ac:dyDescent="0.25">
@@ -24913,7 +24913,7 @@
         <v>1934</v>
       </c>
       <c r="G807" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="808" spans="1:7" x14ac:dyDescent="0.25">
@@ -24936,7 +24936,7 @@
         <v>687</v>
       </c>
       <c r="G808" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="809" spans="1:7" x14ac:dyDescent="0.25">
@@ -24959,7 +24959,7 @@
         <v>680</v>
       </c>
       <c r="G809" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="810" spans="1:7" x14ac:dyDescent="0.25">
@@ -24982,7 +24982,7 @@
         <v>1945</v>
       </c>
       <c r="G810" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="811" spans="1:7" x14ac:dyDescent="0.25">
@@ -25005,7 +25005,7 @@
         <v>1945</v>
       </c>
       <c r="G811" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="812" spans="1:7" x14ac:dyDescent="0.25">
@@ -25028,7 +25028,7 @@
         <v>1945</v>
       </c>
       <c r="G812" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="813" spans="1:7" x14ac:dyDescent="0.25">
@@ -25051,7 +25051,7 @@
         <v>1945</v>
       </c>
       <c r="G813" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="814" spans="1:7" x14ac:dyDescent="0.25">
@@ -25074,7 +25074,7 @@
         <v>1956</v>
       </c>
       <c r="G814" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="815" spans="1:7" x14ac:dyDescent="0.25">
@@ -25097,7 +25097,7 @@
         <v>1956</v>
       </c>
       <c r="G815" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="816" spans="1:7" x14ac:dyDescent="0.25">
@@ -25120,7 +25120,7 @@
         <v>1956</v>
       </c>
       <c r="G816" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="817" spans="1:7" x14ac:dyDescent="0.25">
@@ -25143,7 +25143,7 @@
         <v>1956</v>
       </c>
       <c r="G817" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="818" spans="1:7" x14ac:dyDescent="0.25">
@@ -25166,7 +25166,7 @@
         <v>1956</v>
       </c>
       <c r="G818" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="819" spans="1:7" x14ac:dyDescent="0.25">
@@ -25189,7 +25189,7 @@
         <v>1956</v>
       </c>
       <c r="G819" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="820" spans="1:7" x14ac:dyDescent="0.25">
@@ -25212,7 +25212,7 @@
         <v>1969</v>
       </c>
       <c r="G820" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="821" spans="1:7" x14ac:dyDescent="0.25">
@@ -25235,7 +25235,7 @@
         <v>1969</v>
       </c>
       <c r="G821" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="822" spans="1:7" x14ac:dyDescent="0.25">
@@ -25258,7 +25258,7 @@
         <v>1969</v>
       </c>
       <c r="G822" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="823" spans="1:7" x14ac:dyDescent="0.25">
@@ -25281,7 +25281,7 @@
         <v>1969</v>
       </c>
       <c r="G823" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="824" spans="1:7" x14ac:dyDescent="0.25">
@@ -25304,7 +25304,7 @@
         <v>1969</v>
       </c>
       <c r="G824" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="825" spans="1:7" x14ac:dyDescent="0.25">
@@ -25327,7 +25327,7 @@
         <v>1969</v>
       </c>
       <c r="G825" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="826" spans="1:7" x14ac:dyDescent="0.25">
@@ -25350,7 +25350,7 @@
         <v>1969</v>
       </c>
       <c r="G826" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="827" spans="1:7" x14ac:dyDescent="0.25">
@@ -25373,7 +25373,7 @@
         <v>1969</v>
       </c>
       <c r="G827" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="828" spans="1:7" x14ac:dyDescent="0.25">
@@ -25396,7 +25396,7 @@
         <v>398</v>
       </c>
       <c r="G828" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="829" spans="1:7" x14ac:dyDescent="0.25">
@@ -25419,7 +25419,7 @@
         <v>1367</v>
       </c>
       <c r="G829" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="830" spans="1:7" x14ac:dyDescent="0.25">
@@ -25442,7 +25442,7 @@
         <v>1367</v>
       </c>
       <c r="G830" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="831" spans="1:7" x14ac:dyDescent="0.25">
@@ -25465,7 +25465,7 @@
         <v>892</v>
       </c>
       <c r="G831" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="832" spans="1:7" x14ac:dyDescent="0.25">
@@ -25488,7 +25488,7 @@
         <v>640</v>
       </c>
       <c r="G832" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="833" spans="1:7" x14ac:dyDescent="0.25">
@@ -25511,7 +25511,7 @@
         <v>1999</v>
       </c>
       <c r="G833" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="834" spans="1:7" x14ac:dyDescent="0.25">
@@ -25534,7 +25534,7 @@
         <v>1999</v>
       </c>
       <c r="G834" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="835" spans="1:7" x14ac:dyDescent="0.25">
@@ -25557,7 +25557,7 @@
         <v>1999</v>
       </c>
       <c r="G835" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="836" spans="1:7" x14ac:dyDescent="0.25">
@@ -25580,7 +25580,7 @@
         <v>1999</v>
       </c>
       <c r="G836" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="837" spans="1:7" x14ac:dyDescent="0.25">
@@ -25603,7 +25603,7 @@
         <v>1999</v>
       </c>
       <c r="G837" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
